--- a/research/traditional_assets/database/data/poland/poland_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_beverage_alcoholic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08353296383407285</v>
+        <v>0.08341070120278812</v>
       </c>
       <c r="C2">
-        <v>165.5139642830083</v>
+        <v>164.0252769087011</v>
       </c>
       <c r="D2">
-        <v>156.8739642830083</v>
+        <v>157.0522769087011</v>
       </c>
       <c r="E2">
-        <v>-31.9</v>
+        <v>-30.233</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="G2">
         <v>8.640000000000001</v>
@@ -1451,28 +1451,28 @@
         <v>20.31</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08385010000000001</v>
       </c>
       <c r="N2">
-        <v>20.31</v>
+        <v>20.2261499</v>
       </c>
       <c r="O2">
-        <v>3.8589</v>
+        <v>3.842968481</v>
       </c>
       <c r="P2">
-        <v>16.4511</v>
+        <v>16.383181419</v>
       </c>
       <c r="Q2">
-        <v>24.3411</v>
+        <v>24.273181419</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08353296383407285</v>
+        <v>0.08384168808362437</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905985</v>
+        <v>0.6967468769406125</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>242.2179579988575</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08341070120278812</v>
+        <v>0.08328843857150339</v>
       </c>
       <c r="C3">
-        <v>164.0252769087011</v>
+        <v>162.5369953579397</v>
       </c>
       <c r="D3">
-        <v>157.0522769087011</v>
+        <v>157.2309953579397</v>
       </c>
       <c r="E3">
-        <v>-30.233</v>
+        <v>-28.566</v>
       </c>
       <c r="F3">
-        <v>1.667</v>
+        <v>3.334000000000001</v>
       </c>
       <c r="G3">
         <v>8.640000000000001</v>
@@ -1533,28 +1533,28 @@
         <v>20.31</v>
       </c>
       <c r="M3">
-        <v>0.08385010000000001</v>
+        <v>0.1677002</v>
       </c>
       <c r="N3">
-        <v>20.2261499</v>
+        <v>20.1422998</v>
       </c>
       <c r="O3">
-        <v>3.842968481</v>
+        <v>3.827036962</v>
       </c>
       <c r="P3">
-        <v>16.383181419</v>
+        <v>16.315262838</v>
       </c>
       <c r="Q3">
-        <v>24.273181419</v>
+        <v>24.205262838</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08384168808362437</v>
+        <v>0.08415671282806468</v>
       </c>
       <c r="T3">
-        <v>0.6967468769406125</v>
+        <v>0.7025166657671574</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>242.2179579988575</v>
+        <v>121.1089789994287</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08328843857150339</v>
+        <v>0.08316617594021866</v>
       </c>
       <c r="C4">
-        <v>162.5369953579397</v>
+        <v>161.0491210177294</v>
       </c>
       <c r="D4">
-        <v>157.2309953579397</v>
+        <v>157.4101210177294</v>
       </c>
       <c r="E4">
-        <v>-28.566</v>
+        <v>-26.899</v>
       </c>
       <c r="F4">
-        <v>3.334000000000001</v>
+        <v>5.001</v>
       </c>
       <c r="G4">
         <v>8.640000000000001</v>
@@ -1615,28 +1615,28 @@
         <v>20.31</v>
       </c>
       <c r="M4">
-        <v>0.1677002</v>
+        <v>0.2515503</v>
       </c>
       <c r="N4">
-        <v>20.1422998</v>
+        <v>20.0584497</v>
       </c>
       <c r="O4">
-        <v>3.827036962</v>
+        <v>3.811105442999999</v>
       </c>
       <c r="P4">
-        <v>16.315262838</v>
+        <v>16.247344257</v>
       </c>
       <c r="Q4">
-        <v>24.205262838</v>
+        <v>24.137344257</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08415671282806468</v>
+        <v>0.08447823292806048</v>
       </c>
       <c r="T4">
-        <v>0.7025166657671574</v>
+        <v>0.7084054193117755</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>121.1089789994287</v>
+        <v>80.73931933295248</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08316617594021866</v>
+        <v>0.08304391330893392</v>
       </c>
       <c r="C5">
-        <v>161.0491210177294</v>
+        <v>159.5616552814034</v>
       </c>
       <c r="D5">
-        <v>157.4101210177294</v>
+        <v>157.5896552814034</v>
       </c>
       <c r="E5">
-        <v>-26.899</v>
+        <v>-25.232</v>
       </c>
       <c r="F5">
-        <v>5.001</v>
+        <v>6.668000000000001</v>
       </c>
       <c r="G5">
         <v>8.640000000000001</v>
@@ -1697,28 +1697,28 @@
         <v>20.31</v>
       </c>
       <c r="M5">
-        <v>0.2515503</v>
+        <v>0.3354004</v>
       </c>
       <c r="N5">
-        <v>20.0584497</v>
+        <v>19.9745996</v>
       </c>
       <c r="O5">
-        <v>3.811105442999999</v>
+        <v>3.795173924</v>
       </c>
       <c r="P5">
-        <v>16.247344257</v>
+        <v>16.179425676</v>
       </c>
       <c r="Q5">
-        <v>24.137344257</v>
+        <v>24.069425676</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08447823292806048</v>
+        <v>0.08480645136347283</v>
       </c>
       <c r="T5">
-        <v>0.7084054193117755</v>
+        <v>0.7144168552219062</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>80.73931933295248</v>
+        <v>60.55448949971436</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08304391330893392</v>
+        <v>0.08292165067764917</v>
       </c>
       <c r="C6">
-        <v>159.5616552814034</v>
+        <v>158.0745995486587</v>
       </c>
       <c r="D6">
-        <v>157.5896552814034</v>
+        <v>157.7695995486587</v>
       </c>
       <c r="E6">
-        <v>-25.232</v>
+        <v>-23.565</v>
       </c>
       <c r="F6">
-        <v>6.668000000000001</v>
+        <v>8.335000000000001</v>
       </c>
       <c r="G6">
         <v>8.640000000000001</v>
@@ -1779,28 +1779,28 @@
         <v>20.31</v>
       </c>
       <c r="M6">
-        <v>0.3354004</v>
+        <v>0.4192505</v>
       </c>
       <c r="N6">
-        <v>19.9745996</v>
+        <v>19.8907495</v>
       </c>
       <c r="O6">
-        <v>3.795173924</v>
+        <v>3.779242405</v>
       </c>
       <c r="P6">
-        <v>16.179425676</v>
+        <v>16.111507095</v>
       </c>
       <c r="Q6">
-        <v>24.069425676</v>
+        <v>24.001507095</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08480645136347283</v>
+        <v>0.08514157966068334</v>
       </c>
       <c r="T6">
-        <v>0.7144168552219062</v>
+        <v>0.7205548476775134</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>60.55448949971436</v>
+        <v>48.44359159977149</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08292165067764917</v>
+        <v>0.08279938804636441</v>
       </c>
       <c r="C7">
-        <v>158.0745995486587</v>
+        <v>156.5879552255928</v>
       </c>
       <c r="D7">
-        <v>157.7695995486587</v>
+        <v>157.9499552255928</v>
       </c>
       <c r="E7">
-        <v>-23.565</v>
+        <v>-21.898</v>
       </c>
       <c r="F7">
-        <v>8.335000000000001</v>
+        <v>10.002</v>
       </c>
       <c r="G7">
         <v>8.640000000000001</v>
@@ -1861,28 +1861,28 @@
         <v>20.31</v>
       </c>
       <c r="M7">
-        <v>0.4192505</v>
+        <v>0.5031006000000001</v>
       </c>
       <c r="N7">
-        <v>19.8907495</v>
+        <v>19.8068994</v>
       </c>
       <c r="O7">
-        <v>3.779242405</v>
+        <v>3.763310886</v>
       </c>
       <c r="P7">
-        <v>16.111507095</v>
+        <v>16.043588514</v>
       </c>
       <c r="Q7">
-        <v>24.001507095</v>
+        <v>23.933588514</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08514157966068334</v>
+        <v>0.08548383834719619</v>
       </c>
       <c r="T7">
-        <v>0.7205548476775134</v>
+        <v>0.7268234357172826</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>48.44359159977149</v>
+        <v>40.36965966647624</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08279938804636441</v>
+        <v>0.08267712541507971</v>
       </c>
       <c r="C8">
-        <v>156.5879552255928</v>
+        <v>155.1017237247398</v>
       </c>
       <c r="D8">
-        <v>157.9499552255928</v>
+        <v>158.1307237247398</v>
       </c>
       <c r="E8">
-        <v>-21.898</v>
+        <v>-20.231</v>
       </c>
       <c r="F8">
-        <v>10.002</v>
+        <v>11.669</v>
       </c>
       <c r="G8">
         <v>8.640000000000001</v>
@@ -1943,28 +1943,28 @@
         <v>20.31</v>
       </c>
       <c r="M8">
-        <v>0.5031006</v>
+        <v>0.5869507</v>
       </c>
       <c r="N8">
-        <v>19.8068994</v>
+        <v>19.7230493</v>
       </c>
       <c r="O8">
-        <v>3.763310886</v>
+        <v>3.747379367</v>
       </c>
       <c r="P8">
-        <v>16.043588514</v>
+        <v>15.975669933</v>
       </c>
       <c r="Q8">
-        <v>23.933588514</v>
+        <v>23.865669933</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08548383834719619</v>
+        <v>0.08583345743556957</v>
       </c>
       <c r="T8">
-        <v>0.7268234357172826</v>
+        <v>0.7332268321019931</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>40.36965966647625</v>
+        <v>34.60256542840821</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0826771254150797</v>
+        <v>0.08255486278379497</v>
       </c>
       <c r="C9">
-        <v>155.1017237247399</v>
+        <v>153.615906465108</v>
       </c>
       <c r="D9">
-        <v>158.1307237247399</v>
+        <v>158.3119064651081</v>
       </c>
       <c r="E9">
-        <v>-20.23099999999999</v>
+        <v>-18.564</v>
       </c>
       <c r="F9">
-        <v>11.669</v>
+        <v>13.336</v>
       </c>
       <c r="G9">
         <v>8.640000000000001</v>
@@ -2025,28 +2025,28 @@
         <v>20.31</v>
       </c>
       <c r="M9">
-        <v>0.5869507</v>
+        <v>0.6708008000000001</v>
       </c>
       <c r="N9">
-        <v>19.7230493</v>
+        <v>19.6391992</v>
       </c>
       <c r="O9">
-        <v>3.747379367</v>
+        <v>3.731447848</v>
       </c>
       <c r="P9">
-        <v>15.975669933</v>
+        <v>15.907751352</v>
       </c>
       <c r="Q9">
-        <v>23.865669933</v>
+        <v>23.797751352</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08583345743556957</v>
+        <v>0.08619067693890757</v>
       </c>
       <c r="T9">
-        <v>0.7332268321019931</v>
+        <v>0.7397694327559364</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.60256542840821</v>
+        <v>30.27724474985718</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08255486278379497</v>
+        <v>0.08243260015251022</v>
       </c>
       <c r="C10">
-        <v>153.615906465108</v>
+        <v>152.1305048722165</v>
       </c>
       <c r="D10">
-        <v>158.3119064651081</v>
+        <v>158.4935048722165</v>
       </c>
       <c r="E10">
-        <v>-18.564</v>
+        <v>-16.897</v>
       </c>
       <c r="F10">
-        <v>13.336</v>
+        <v>15.003</v>
       </c>
       <c r="G10">
         <v>8.640000000000001</v>
@@ -2107,28 +2107,28 @@
         <v>20.31</v>
       </c>
       <c r="M10">
-        <v>0.6708008000000001</v>
+        <v>0.7546509</v>
       </c>
       <c r="N10">
-        <v>19.6391992</v>
+        <v>19.5553491</v>
       </c>
       <c r="O10">
-        <v>3.731447848</v>
+        <v>3.715516329</v>
       </c>
       <c r="P10">
-        <v>15.907751352</v>
+        <v>15.839832771</v>
       </c>
       <c r="Q10">
-        <v>23.797751352</v>
+        <v>23.729832771</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08619067693890757</v>
+        <v>0.08655574742034089</v>
       </c>
       <c r="T10">
-        <v>0.7397694327559364</v>
+        <v>0.7464558268308453</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.27724474985718</v>
+        <v>26.9131064443175</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08243260015251022</v>
+        <v>0.08231033752122548</v>
       </c>
       <c r="C11">
-        <v>152.1305048722165</v>
+        <v>150.6455203781324</v>
       </c>
       <c r="D11">
-        <v>158.4935048722165</v>
+        <v>158.6755203781324</v>
       </c>
       <c r="E11">
-        <v>-16.897</v>
+        <v>-15.23</v>
       </c>
       <c r="F11">
-        <v>15.003</v>
+        <v>16.67</v>
       </c>
       <c r="G11">
         <v>8.640000000000001</v>
@@ -2189,28 +2189,28 @@
         <v>20.31</v>
       </c>
       <c r="M11">
-        <v>0.7546509</v>
+        <v>0.8385010000000001</v>
       </c>
       <c r="N11">
-        <v>19.5553491</v>
+        <v>19.471499</v>
       </c>
       <c r="O11">
-        <v>3.715516329</v>
+        <v>3.69958481</v>
       </c>
       <c r="P11">
-        <v>15.839832771</v>
+        <v>15.77191419</v>
       </c>
       <c r="Q11">
-        <v>23.729832771</v>
+        <v>23.66191419</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08655574742034089</v>
+        <v>0.08692893057913942</v>
       </c>
       <c r="T11">
-        <v>0.7464558268308453</v>
+        <v>0.7532908074407524</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.9131064443175</v>
+        <v>24.22179579988574</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08231033752122548</v>
+        <v>0.08218807488994075</v>
       </c>
       <c r="C12">
-        <v>150.6455203781324</v>
+        <v>149.1609544215092</v>
       </c>
       <c r="D12">
-        <v>158.6755203781324</v>
+        <v>158.8579544215092</v>
       </c>
       <c r="E12">
-        <v>-15.23</v>
+        <v>-13.563</v>
       </c>
       <c r="F12">
-        <v>16.67</v>
+        <v>18.337</v>
       </c>
       <c r="G12">
         <v>8.640000000000001</v>
@@ -2271,28 +2271,28 @@
         <v>20.31</v>
       </c>
       <c r="M12">
-        <v>0.8385010000000001</v>
+        <v>0.9223511000000001</v>
       </c>
       <c r="N12">
-        <v>19.471499</v>
+        <v>19.3876489</v>
       </c>
       <c r="O12">
-        <v>3.69958481</v>
+        <v>3.683653291</v>
       </c>
       <c r="P12">
-        <v>15.77191419</v>
+        <v>15.703995609</v>
       </c>
       <c r="Q12">
-        <v>23.66191419</v>
+        <v>23.593995609</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08692893057913942</v>
+        <v>0.0873104998763379</v>
       </c>
       <c r="T12">
-        <v>0.7532908074407524</v>
+        <v>0.7602793831205449</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.22179579988574</v>
+        <v>22.01981436353249</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08218807488994075</v>
+        <v>0.082065812258656</v>
       </c>
       <c r="C13">
-        <v>149.1609544215092</v>
+        <v>147.6768084476242</v>
       </c>
       <c r="D13">
-        <v>158.8579544215092</v>
+        <v>159.0408084476242</v>
       </c>
       <c r="E13">
-        <v>-13.563</v>
+        <v>-11.896</v>
       </c>
       <c r="F13">
-        <v>18.337</v>
+        <v>20.004</v>
       </c>
       <c r="G13">
         <v>8.640000000000001</v>
@@ -2353,28 +2353,28 @@
         <v>20.31</v>
       </c>
       <c r="M13">
-        <v>0.9223511000000001</v>
+        <v>1.0062012</v>
       </c>
       <c r="N13">
-        <v>19.3876489</v>
+        <v>19.3037988</v>
       </c>
       <c r="O13">
-        <v>3.683653291</v>
+        <v>3.667721772</v>
       </c>
       <c r="P13">
-        <v>15.703995609</v>
+        <v>15.636077028</v>
       </c>
       <c r="Q13">
-        <v>23.593995609</v>
+        <v>23.526077028</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0873104998763379</v>
+        <v>0.08770074120301818</v>
       </c>
       <c r="T13">
-        <v>0.7602793831205449</v>
+        <v>0.7674267900657873</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.01981436353249</v>
+        <v>20.18482983323812</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.082065812258656</v>
+        <v>0.08194354962737127</v>
       </c>
       <c r="C14">
-        <v>147.6768084476242</v>
+        <v>146.1930839084164</v>
       </c>
       <c r="D14">
-        <v>159.0408084476242</v>
+        <v>159.2240839084164</v>
       </c>
       <c r="E14">
-        <v>-11.896</v>
+        <v>-10.229</v>
       </c>
       <c r="F14">
-        <v>20.004</v>
+        <v>21.671</v>
       </c>
       <c r="G14">
         <v>8.640000000000001</v>
@@ -2435,28 +2435,28 @@
         <v>20.31</v>
       </c>
       <c r="M14">
-        <v>1.0062012</v>
+        <v>1.0900513</v>
       </c>
       <c r="N14">
-        <v>19.3037988</v>
+        <v>19.2199487</v>
       </c>
       <c r="O14">
-        <v>3.667721772</v>
+        <v>3.651790253</v>
       </c>
       <c r="P14">
-        <v>15.636077028</v>
+        <v>15.568158447</v>
       </c>
       <c r="Q14">
-        <v>23.526077028</v>
+        <v>23.458158447</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08770074120301818</v>
+        <v>0.08809995359467962</v>
       </c>
       <c r="T14">
-        <v>0.7674267900657873</v>
+        <v>0.7747385052166675</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.18482983323812</v>
+        <v>18.63215061529673</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08194354962737127</v>
+        <v>0.08182128699608654</v>
       </c>
       <c r="C15">
-        <v>146.1930839084164</v>
+        <v>144.7097822625256</v>
       </c>
       <c r="D15">
-        <v>159.2240839084164</v>
+        <v>159.4077822625256</v>
       </c>
       <c r="E15">
-        <v>-10.229</v>
+        <v>-8.561999999999994</v>
       </c>
       <c r="F15">
-        <v>21.671</v>
+        <v>23.338</v>
       </c>
       <c r="G15">
         <v>8.640000000000001</v>
@@ -2517,28 +2517,28 @@
         <v>20.31</v>
       </c>
       <c r="M15">
-        <v>1.0900513</v>
+        <v>1.1739014</v>
       </c>
       <c r="N15">
-        <v>19.2199487</v>
+        <v>19.1360986</v>
       </c>
       <c r="O15">
-        <v>3.651790253</v>
+        <v>3.635858733999999</v>
       </c>
       <c r="P15">
-        <v>15.568158447</v>
+        <v>15.500239866</v>
       </c>
       <c r="Q15">
-        <v>23.458158447</v>
+        <v>23.390239866</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08809995359467962</v>
+        <v>0.08850844999544946</v>
       </c>
       <c r="T15">
-        <v>0.7747385052166675</v>
+        <v>0.7822202602547775</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.63215061529673</v>
+        <v>17.3012827142041</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08182128699608654</v>
+        <v>0.08169902436480178</v>
       </c>
       <c r="C16">
-        <v>144.7097822625256</v>
+        <v>143.2269049753307</v>
       </c>
       <c r="D16">
-        <v>159.4077822625256</v>
+        <v>159.5919049753307</v>
       </c>
       <c r="E16">
-        <v>-8.561999999999994</v>
+        <v>-6.894999999999992</v>
       </c>
       <c r="F16">
-        <v>23.338</v>
+        <v>25.00500000000001</v>
       </c>
       <c r="G16">
         <v>8.640000000000001</v>
@@ -2599,28 +2599,28 @@
         <v>20.31</v>
       </c>
       <c r="M16">
-        <v>1.1739014</v>
+        <v>1.2577515</v>
       </c>
       <c r="N16">
-        <v>19.1360986</v>
+        <v>19.0522485</v>
       </c>
       <c r="O16">
-        <v>3.635858733999999</v>
+        <v>3.619927215</v>
       </c>
       <c r="P16">
-        <v>15.500239866</v>
+        <v>15.432321285</v>
       </c>
       <c r="Q16">
-        <v>23.390239866</v>
+        <v>23.322321285</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08850844999544946</v>
+        <v>0.08892655807623739</v>
       </c>
       <c r="T16">
-        <v>0.7822202602547775</v>
+        <v>0.7898780565879018</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.3012827142041</v>
+        <v>16.14786386659049</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08169902436480178</v>
+        <v>0.08157676173351706</v>
       </c>
       <c r="C17">
-        <v>143.2269049753307</v>
+        <v>141.7444535189887</v>
       </c>
       <c r="D17">
-        <v>159.5919049753307</v>
+        <v>159.7764535189887</v>
       </c>
       <c r="E17">
-        <v>-6.894999999999996</v>
+        <v>-5.227999999999994</v>
       </c>
       <c r="F17">
-        <v>25.005</v>
+        <v>26.672</v>
       </c>
       <c r="G17">
         <v>8.640000000000001</v>
@@ -2681,28 +2681,28 @@
         <v>20.31</v>
       </c>
       <c r="M17">
-        <v>1.2577515</v>
+        <v>1.3416016</v>
       </c>
       <c r="N17">
-        <v>19.0522485</v>
+        <v>18.9683984</v>
       </c>
       <c r="O17">
-        <v>3.619927215</v>
+        <v>3.603995696</v>
       </c>
       <c r="P17">
-        <v>15.432321285</v>
+        <v>15.364402704</v>
       </c>
       <c r="Q17">
-        <v>23.322321285</v>
+        <v>23.254402704</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08892655807623739</v>
+        <v>0.08935462111132983</v>
       </c>
       <c r="T17">
-        <v>0.7898780565879018</v>
+        <v>0.7977181814051481</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.14786386659049</v>
+        <v>15.13862237492859</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08157676173351706</v>
+        <v>0.08145449910223232</v>
       </c>
       <c r="C18">
-        <v>141.7444535189887</v>
+        <v>140.2624293724739</v>
       </c>
       <c r="D18">
-        <v>159.7764535189887</v>
+        <v>159.9614293724739</v>
       </c>
       <c r="E18">
-        <v>-5.227999999999994</v>
+        <v>-3.560999999999993</v>
       </c>
       <c r="F18">
-        <v>26.672</v>
+        <v>28.33900000000001</v>
       </c>
       <c r="G18">
         <v>8.640000000000001</v>
@@ -2763,28 +2763,28 @@
         <v>20.31</v>
       </c>
       <c r="M18">
-        <v>1.3416016</v>
+        <v>1.4254517</v>
       </c>
       <c r="N18">
-        <v>18.9683984</v>
+        <v>18.8845483</v>
       </c>
       <c r="O18">
-        <v>3.603995696</v>
+        <v>3.588064177</v>
       </c>
       <c r="P18">
-        <v>15.364402704</v>
+        <v>15.296484123</v>
       </c>
       <c r="Q18">
-        <v>23.254402704</v>
+        <v>23.186484123</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08935462111132983</v>
+        <v>0.08979299891835218</v>
       </c>
       <c r="T18">
-        <v>0.7977181814051481</v>
+        <v>0.8057472248926895</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.13862237492859</v>
+        <v>14.24811517640338</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08145449910223232</v>
+        <v>0.08133223647094757</v>
       </c>
       <c r="C19">
-        <v>140.2624293724739</v>
+        <v>138.7808340216175</v>
       </c>
       <c r="D19">
-        <v>159.9614293724739</v>
+        <v>160.1468340216175</v>
       </c>
       <c r="E19">
-        <v>-3.560999999999993</v>
+        <v>-1.893999999999991</v>
       </c>
       <c r="F19">
-        <v>28.33900000000001</v>
+        <v>30.00600000000001</v>
       </c>
       <c r="G19">
         <v>8.640000000000001</v>
@@ -2845,28 +2845,28 @@
         <v>20.31</v>
       </c>
       <c r="M19">
-        <v>1.4254517</v>
+        <v>1.5093018</v>
       </c>
       <c r="N19">
-        <v>18.8845483</v>
+        <v>18.8006982</v>
       </c>
       <c r="O19">
-        <v>3.588064177</v>
+        <v>3.572132658</v>
       </c>
       <c r="P19">
-        <v>15.296484123</v>
+        <v>15.228565542</v>
       </c>
       <c r="Q19">
-        <v>23.186484123</v>
+        <v>23.118565542</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08979299891835218</v>
+        <v>0.09024206886700924</v>
       </c>
       <c r="T19">
-        <v>0.8057472248926895</v>
+        <v>0.8139720987091952</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.24811517640338</v>
+        <v>13.45655322215875</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08133223647094759</v>
+        <v>0.08144082383966283</v>
       </c>
       <c r="C20">
-        <v>138.7808340216174</v>
+        <v>136.9491458405869</v>
       </c>
       <c r="D20">
-        <v>160.1468340216175</v>
+        <v>159.9821458405869</v>
       </c>
       <c r="E20">
-        <v>-1.893999999999998</v>
+        <v>-0.2269999999999932</v>
       </c>
       <c r="F20">
-        <v>30.006</v>
+        <v>31.67300000000001</v>
       </c>
       <c r="G20">
         <v>8.640000000000001</v>
@@ -2927,45 +2927,45 @@
         <v>20.31</v>
       </c>
       <c r="M20">
-        <v>1.5093018</v>
+        <v>1.6406614</v>
       </c>
       <c r="N20">
-        <v>18.8006982</v>
+        <v>18.6693386</v>
       </c>
       <c r="O20">
-        <v>3.572132658</v>
+        <v>3.547174334</v>
       </c>
       <c r="P20">
-        <v>15.228565542</v>
+        <v>15.122164266</v>
       </c>
       <c r="Q20">
-        <v>23.118565542</v>
+        <v>23.012164266</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09024206886700924</v>
+        <v>0.09070222696254671</v>
       </c>
       <c r="T20">
-        <v>0.8139720987091952</v>
+        <v>0.8224000558298122</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.19</v>
       </c>
       <c r="W20">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.45655322215875</v>
+        <v>12.37915391926695</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08144082383966283</v>
+        <v>0.08133071120837811</v>
       </c>
       <c r="C21">
-        <v>136.9491458405869</v>
+        <v>135.4491497139386</v>
       </c>
       <c r="D21">
-        <v>159.9821458405869</v>
+        <v>160.1491497139386</v>
       </c>
       <c r="E21">
-        <v>-0.2269999999999932</v>
+        <v>1.440000000000005</v>
       </c>
       <c r="F21">
-        <v>31.67300000000001</v>
+        <v>33.34</v>
       </c>
       <c r="G21">
         <v>8.640000000000001</v>
@@ -3009,28 +3009,28 @@
         <v>20.31</v>
       </c>
       <c r="M21">
-        <v>1.6406614</v>
+        <v>1.727012</v>
       </c>
       <c r="N21">
-        <v>18.6693386</v>
+        <v>18.582988</v>
       </c>
       <c r="O21">
-        <v>3.547174334</v>
+        <v>3.53076772</v>
       </c>
       <c r="P21">
-        <v>15.122164266</v>
+        <v>15.05222028</v>
       </c>
       <c r="Q21">
-        <v>23.012164266</v>
+        <v>22.94222028</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09070222696254671</v>
+        <v>0.09117388901047263</v>
       </c>
       <c r="T21">
-        <v>0.8224000558298122</v>
+        <v>0.8310387118784448</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.37915391926695</v>
+        <v>11.7601962233036</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08133071120837811</v>
+        <v>0.08122059857709336</v>
       </c>
       <c r="C22">
-        <v>135.4491497139386</v>
+        <v>133.9495026192202</v>
       </c>
       <c r="D22">
-        <v>160.1491497139386</v>
+        <v>160.3165026192202</v>
       </c>
       <c r="E22">
-        <v>1.440000000000005</v>
+        <v>3.107000000000006</v>
       </c>
       <c r="F22">
-        <v>33.34</v>
+        <v>35.00700000000001</v>
       </c>
       <c r="G22">
         <v>8.640000000000001</v>
@@ -3091,28 +3091,28 @@
         <v>20.31</v>
       </c>
       <c r="M22">
-        <v>1.727012</v>
+        <v>1.8133626</v>
       </c>
       <c r="N22">
-        <v>18.582988</v>
+        <v>18.4966374</v>
       </c>
       <c r="O22">
-        <v>3.53076772</v>
+        <v>3.514361106</v>
       </c>
       <c r="P22">
-        <v>15.05222028</v>
+        <v>14.982276294</v>
       </c>
       <c r="Q22">
-        <v>22.94222028</v>
+        <v>22.872276294</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09117388901047263</v>
+        <v>0.09165749186973843</v>
       </c>
       <c r="T22">
-        <v>0.8310387118784448</v>
+        <v>0.8398960680802072</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.7601962233036</v>
+        <v>11.20018687933676</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08122059857709336</v>
+        <v>0.08111048594580862</v>
       </c>
       <c r="C23">
-        <v>133.9495026192202</v>
+        <v>132.4502056517722</v>
       </c>
       <c r="D23">
-        <v>160.3165026192202</v>
+        <v>160.4842056517722</v>
       </c>
       <c r="E23">
-        <v>3.107000000000006</v>
+        <v>4.774000000000008</v>
       </c>
       <c r="F23">
-        <v>35.00700000000001</v>
+        <v>36.67400000000001</v>
       </c>
       <c r="G23">
         <v>8.640000000000001</v>
@@ -3173,28 +3173,28 @@
         <v>20.31</v>
       </c>
       <c r="M23">
-        <v>1.8133626</v>
+        <v>1.8997132</v>
       </c>
       <c r="N23">
-        <v>18.4966374</v>
+        <v>18.4102868</v>
       </c>
       <c r="O23">
-        <v>3.514361106</v>
+        <v>3.497954492</v>
       </c>
       <c r="P23">
-        <v>14.982276294</v>
+        <v>14.912332308</v>
       </c>
       <c r="Q23">
-        <v>22.872276294</v>
+        <v>22.802332308</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09165749186973843</v>
+        <v>0.09215349480231874</v>
       </c>
       <c r="T23">
-        <v>0.8398960680802072</v>
+        <v>0.8489805359794507</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.20018687933676</v>
+        <v>10.69108747573054</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08111048594580862</v>
+        <v>0.08100037331452389</v>
       </c>
       <c r="C24">
-        <v>132.4502056517722</v>
+        <v>130.9512599115228</v>
       </c>
       <c r="D24">
-        <v>160.4842056517722</v>
+        <v>160.6522599115227</v>
       </c>
       <c r="E24">
-        <v>4.774000000000008</v>
+        <v>6.44100000000001</v>
       </c>
       <c r="F24">
-        <v>36.67400000000001</v>
+        <v>38.34100000000001</v>
       </c>
       <c r="G24">
         <v>8.640000000000001</v>
@@ -3255,28 +3255,28 @@
         <v>20.31</v>
       </c>
       <c r="M24">
-        <v>1.8997132</v>
+        <v>1.9860638</v>
       </c>
       <c r="N24">
-        <v>18.4102868</v>
+        <v>18.3239362</v>
       </c>
       <c r="O24">
-        <v>3.497954492</v>
+        <v>3.481547878</v>
       </c>
       <c r="P24">
-        <v>14.912332308</v>
+        <v>14.842388322</v>
       </c>
       <c r="Q24">
-        <v>22.802332308</v>
+        <v>22.732388322</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09215349480231874</v>
+        <v>0.09266238092795309</v>
       </c>
       <c r="T24">
-        <v>0.8489805359794507</v>
+        <v>0.8583009640838692</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.69108747573054</v>
+        <v>10.22625758548139</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08100037331452389</v>
+        <v>0.08122074068323915</v>
       </c>
       <c r="C25">
-        <v>130.9512599115228</v>
+        <v>128.9482864160871</v>
       </c>
       <c r="D25">
-        <v>160.6522599115227</v>
+        <v>160.3162864160872</v>
       </c>
       <c r="E25">
-        <v>6.44100000000001</v>
+        <v>8.108000000000011</v>
       </c>
       <c r="F25">
-        <v>38.34100000000001</v>
+        <v>40.00800000000001</v>
       </c>
       <c r="G25">
         <v>8.640000000000001</v>
@@ -3337,45 +3337,45 @@
         <v>20.31</v>
       </c>
       <c r="M25">
-        <v>1.9860638</v>
+        <v>2.140428</v>
       </c>
       <c r="N25">
-        <v>18.3239362</v>
+        <v>18.169572</v>
       </c>
       <c r="O25">
-        <v>3.481547878</v>
+        <v>3.45221868</v>
       </c>
       <c r="P25">
-        <v>14.842388322</v>
+        <v>14.71735332</v>
       </c>
       <c r="Q25">
-        <v>22.732388322</v>
+        <v>22.60735332</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09266238092795309</v>
+        <v>0.09318465879373572</v>
       </c>
       <c r="T25">
-        <v>0.8583009640838692</v>
+        <v>0.8678666666120884</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.19</v>
       </c>
       <c r="W25">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>10.22625758548139</v>
+        <v>9.488756454316611</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08122074068323915</v>
+        <v>0.08112439805195441</v>
       </c>
       <c r="C26">
-        <v>128.9482864160871</v>
+        <v>127.4279979635691</v>
       </c>
       <c r="D26">
-        <v>160.3162864160872</v>
+        <v>160.4629979635691</v>
       </c>
       <c r="E26">
-        <v>8.108000000000004</v>
+        <v>9.775000000000006</v>
       </c>
       <c r="F26">
-        <v>40.008</v>
+        <v>41.675</v>
       </c>
       <c r="G26">
         <v>8.640000000000001</v>
@@ -3419,28 +3419,28 @@
         <v>20.31</v>
       </c>
       <c r="M26">
-        <v>2.140428</v>
+        <v>2.2296125</v>
       </c>
       <c r="N26">
-        <v>18.169572</v>
+        <v>18.0803875</v>
       </c>
       <c r="O26">
-        <v>3.45221868</v>
+        <v>3.435273625</v>
       </c>
       <c r="P26">
-        <v>14.71735332</v>
+        <v>14.645113875</v>
       </c>
       <c r="Q26">
-        <v>22.60735332</v>
+        <v>22.535113875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09318465879373572</v>
+        <v>0.09372086406927255</v>
       </c>
       <c r="T26">
-        <v>0.8678666666120884</v>
+        <v>0.8776874545410601</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.488756454316613</v>
+        <v>9.109206196143949</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08112439805195441</v>
+        <v>0.08102805542066967</v>
       </c>
       <c r="C27">
-        <v>127.4279979635691</v>
+        <v>125.9079782796756</v>
       </c>
       <c r="D27">
-        <v>160.4629979635691</v>
+        <v>160.6099782796757</v>
       </c>
       <c r="E27">
-        <v>9.775000000000006</v>
+        <v>11.44200000000001</v>
       </c>
       <c r="F27">
-        <v>41.675</v>
+        <v>43.34200000000001</v>
       </c>
       <c r="G27">
         <v>8.640000000000001</v>
@@ -3501,28 +3501,28 @@
         <v>20.31</v>
       </c>
       <c r="M27">
-        <v>2.2296125</v>
+        <v>2.318797</v>
       </c>
       <c r="N27">
-        <v>18.0803875</v>
+        <v>17.991203</v>
       </c>
       <c r="O27">
-        <v>3.435273625</v>
+        <v>3.41832857</v>
       </c>
       <c r="P27">
-        <v>14.645113875</v>
+        <v>14.57287443</v>
       </c>
       <c r="Q27">
-        <v>22.535113875</v>
+        <v>22.46287443</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09372086406927255</v>
+        <v>0.09427156137928333</v>
       </c>
       <c r="T27">
-        <v>0.8776874545410601</v>
+        <v>0.8877736691708149</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.109206196143949</v>
+        <v>8.758852111676871</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08102805542066967</v>
+        <v>0.08093171278938492</v>
       </c>
       <c r="C28">
-        <v>125.9079782796756</v>
+        <v>124.3882281036409</v>
       </c>
       <c r="D28">
-        <v>160.6099782796757</v>
+        <v>160.7572281036409</v>
       </c>
       <c r="E28">
-        <v>11.44200000000001</v>
+        <v>13.10900000000001</v>
       </c>
       <c r="F28">
-        <v>43.34200000000001</v>
+        <v>45.00900000000001</v>
       </c>
       <c r="G28">
         <v>8.640000000000001</v>
@@ -3583,28 +3583,28 @@
         <v>20.31</v>
       </c>
       <c r="M28">
-        <v>2.318797</v>
+        <v>2.4079815</v>
       </c>
       <c r="N28">
-        <v>17.991203</v>
+        <v>17.9020185</v>
       </c>
       <c r="O28">
-        <v>3.41832857</v>
+        <v>3.401383515</v>
       </c>
       <c r="P28">
-        <v>14.57287443</v>
+        <v>14.500634985</v>
       </c>
       <c r="Q28">
-        <v>22.46287443</v>
+        <v>22.390634985</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09427156137928333</v>
+        <v>0.09483734628682866</v>
       </c>
       <c r="T28">
-        <v>0.8877736691708149</v>
+        <v>0.89813621844796</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.758852111676871</v>
+        <v>8.434450181614764</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08093171278938492</v>
+        <v>0.08083537015810019</v>
       </c>
       <c r="C29">
-        <v>124.3882281036409</v>
+        <v>122.8687481774127</v>
       </c>
       <c r="D29">
-        <v>160.7572281036409</v>
+        <v>160.9047481774127</v>
       </c>
       <c r="E29">
-        <v>13.10900000000001</v>
+        <v>14.77600000000001</v>
       </c>
       <c r="F29">
-        <v>45.00900000000001</v>
+        <v>46.67600000000001</v>
       </c>
       <c r="G29">
         <v>8.640000000000001</v>
@@ -3665,28 +3665,28 @@
         <v>20.31</v>
       </c>
       <c r="M29">
-        <v>2.4079815</v>
+        <v>2.497166</v>
       </c>
       <c r="N29">
-        <v>17.9020185</v>
+        <v>17.812834</v>
       </c>
       <c r="O29">
-        <v>3.401383515</v>
+        <v>3.38443846</v>
       </c>
       <c r="P29">
-        <v>14.500634985</v>
+        <v>14.42839554</v>
       </c>
       <c r="Q29">
-        <v>22.390634985</v>
+        <v>22.31839554</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09483734628682866</v>
+        <v>0.09541884744180582</v>
       </c>
       <c r="T29">
-        <v>0.89813621844796</v>
+        <v>0.908786616316137</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.434450181614764</v>
+        <v>8.133219817985667</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08083537015810019</v>
+        <v>0.08073902752681544</v>
       </c>
       <c r="C30">
-        <v>122.8687481774127</v>
+        <v>121.3495392456646</v>
       </c>
       <c r="D30">
-        <v>160.9047481774127</v>
+        <v>161.0525392456647</v>
       </c>
       <c r="E30">
-        <v>14.77600000000001</v>
+        <v>16.44300000000001</v>
       </c>
       <c r="F30">
-        <v>46.67600000000001</v>
+        <v>48.34300000000001</v>
       </c>
       <c r="G30">
         <v>8.640000000000001</v>
@@ -3747,28 +3747,28 @@
         <v>20.31</v>
       </c>
       <c r="M30">
-        <v>2.497166</v>
+        <v>2.5863505</v>
       </c>
       <c r="N30">
-        <v>17.812834</v>
+        <v>17.7236495</v>
       </c>
       <c r="O30">
-        <v>3.38443846</v>
+        <v>3.367493404999999</v>
       </c>
       <c r="P30">
-        <v>14.42839554</v>
+        <v>14.356156095</v>
       </c>
       <c r="Q30">
-        <v>22.31839554</v>
+        <v>22.246156095</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09541884744180582</v>
+        <v>0.09601672891100768</v>
       </c>
       <c r="T30">
-        <v>0.908786616316137</v>
+        <v>0.9197370253918685</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.133219817985667</v>
+        <v>7.852763962193057</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08073902752681544</v>
+        <v>0.08083708489553071</v>
       </c>
       <c r="C31">
-        <v>121.3495392456646</v>
+        <v>119.5321202007567</v>
       </c>
       <c r="D31">
-        <v>161.0525392456647</v>
+        <v>160.9021202007567</v>
       </c>
       <c r="E31">
-        <v>16.443</v>
+        <v>18.11000000000001</v>
       </c>
       <c r="F31">
-        <v>48.343</v>
+        <v>50.01000000000001</v>
       </c>
       <c r="G31">
         <v>8.640000000000001</v>
@@ -3829,45 +3829,45 @@
         <v>20.31</v>
       </c>
       <c r="M31">
-        <v>2.5863505</v>
+        <v>2.715543</v>
       </c>
       <c r="N31">
-        <v>17.7236495</v>
+        <v>17.594457</v>
       </c>
       <c r="O31">
-        <v>3.367493405</v>
+        <v>3.34294683</v>
       </c>
       <c r="P31">
-        <v>14.356156095</v>
+        <v>14.25151017</v>
       </c>
       <c r="Q31">
-        <v>22.246156095</v>
+        <v>22.14151017</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09601672891100768</v>
+        <v>0.09663169270790102</v>
       </c>
       <c r="T31">
-        <v>0.9197370253918683</v>
+        <v>0.9310003032983349</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.19</v>
       </c>
       <c r="W31">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.85276396219306</v>
+        <v>7.479167149995414</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08083708489553071</v>
+        <v>0.08074722226424597</v>
       </c>
       <c r="C32">
-        <v>119.5321202007567</v>
+        <v>118.0029578298562</v>
       </c>
       <c r="D32">
-        <v>160.9021202007567</v>
+        <v>161.0399578298562</v>
       </c>
       <c r="E32">
-        <v>18.11000000000001</v>
+        <v>19.77700000000001</v>
       </c>
       <c r="F32">
-        <v>50.01000000000001</v>
+        <v>51.67700000000001</v>
       </c>
       <c r="G32">
         <v>8.640000000000001</v>
@@ -3911,28 +3911,28 @@
         <v>20.31</v>
       </c>
       <c r="M32">
-        <v>2.715543</v>
+        <v>2.8060611</v>
       </c>
       <c r="N32">
-        <v>17.594457</v>
+        <v>17.5039389</v>
       </c>
       <c r="O32">
-        <v>3.34294683</v>
+        <v>3.325748390999999</v>
       </c>
       <c r="P32">
-        <v>14.25151017</v>
+        <v>14.178190509</v>
       </c>
       <c r="Q32">
-        <v>22.14151017</v>
+        <v>22.068190509</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09663169270790102</v>
+        <v>0.09726448154238547</v>
       </c>
       <c r="T32">
-        <v>0.9310003032983349</v>
+        <v>0.9425900530281772</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.479167149995414</v>
+        <v>7.237903693543949</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08074722226424597</v>
+        <v>0.08065735963296122</v>
       </c>
       <c r="C33">
-        <v>118.0029578298562</v>
+        <v>116.4740318200639</v>
       </c>
       <c r="D33">
-        <v>161.0399578298562</v>
+        <v>161.1780318200639</v>
       </c>
       <c r="E33">
-        <v>19.77700000000001</v>
+        <v>21.44400000000001</v>
       </c>
       <c r="F33">
-        <v>51.67700000000001</v>
+        <v>53.34400000000001</v>
       </c>
       <c r="G33">
         <v>8.640000000000001</v>
@@ -3993,28 +3993,28 @@
         <v>20.31</v>
       </c>
       <c r="M33">
-        <v>2.8060611</v>
+        <v>2.896579200000001</v>
       </c>
       <c r="N33">
-        <v>17.5039389</v>
+        <v>17.4134208</v>
       </c>
       <c r="O33">
-        <v>3.325748390999999</v>
+        <v>3.308549951999999</v>
       </c>
       <c r="P33">
-        <v>14.178190509</v>
+        <v>14.104870848</v>
       </c>
       <c r="Q33">
-        <v>22.068190509</v>
+        <v>21.994870848</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09726448154238547</v>
+        <v>0.09791588181317828</v>
       </c>
       <c r="T33">
-        <v>0.9425900530281772</v>
+        <v>0.9545206777500739</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.237903693543949</v>
+        <v>7.0117192031207</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08065735963296122</v>
+        <v>0.08056749700167649</v>
       </c>
       <c r="C34">
-        <v>116.4740318200639</v>
+        <v>114.9453427798623</v>
       </c>
       <c r="D34">
-        <v>161.1780318200639</v>
+        <v>161.3163427798623</v>
       </c>
       <c r="E34">
-        <v>21.44400000000001</v>
+        <v>23.11100000000001</v>
       </c>
       <c r="F34">
-        <v>53.34400000000001</v>
+        <v>55.01100000000001</v>
       </c>
       <c r="G34">
         <v>8.640000000000001</v>
@@ -4075,28 +4075,28 @@
         <v>20.31</v>
       </c>
       <c r="M34">
-        <v>2.896579200000001</v>
+        <v>2.987097300000001</v>
       </c>
       <c r="N34">
-        <v>17.4134208</v>
+        <v>17.3229027</v>
       </c>
       <c r="O34">
-        <v>3.308549951999999</v>
+        <v>3.291351513</v>
       </c>
       <c r="P34">
-        <v>14.104870848</v>
+        <v>14.031551187</v>
       </c>
       <c r="Q34">
-        <v>21.994870848</v>
+        <v>21.921551187</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09791588181317828</v>
+        <v>0.09858672686817388</v>
       </c>
       <c r="T34">
-        <v>0.9545206777500739</v>
+        <v>0.9668074405233702</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.0117192031207</v>
+        <v>6.799242863632193</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08056749700167649</v>
+        <v>0.08047763437039177</v>
       </c>
       <c r="C35">
-        <v>114.9453427798623</v>
+        <v>113.416891319824</v>
       </c>
       <c r="D35">
-        <v>161.3163427798623</v>
+        <v>161.454891319824</v>
       </c>
       <c r="E35">
-        <v>23.11100000000001</v>
+        <v>24.77800000000001</v>
       </c>
       <c r="F35">
-        <v>55.01100000000001</v>
+        <v>56.67800000000001</v>
       </c>
       <c r="G35">
         <v>8.640000000000001</v>
@@ -4157,28 +4157,28 @@
         <v>20.31</v>
       </c>
       <c r="M35">
-        <v>2.987097300000001</v>
+        <v>3.077615400000001</v>
       </c>
       <c r="N35">
-        <v>17.3229027</v>
+        <v>17.2323846</v>
       </c>
       <c r="O35">
-        <v>3.291351513</v>
+        <v>3.274153073999999</v>
       </c>
       <c r="P35">
-        <v>14.031551187</v>
+        <v>13.958231526</v>
       </c>
       <c r="Q35">
-        <v>21.921551187</v>
+        <v>21.848231526</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09858672686817388</v>
+        <v>0.09927790056119964</v>
       </c>
       <c r="T35">
-        <v>0.9668074405233702</v>
+        <v>0.9794665294413121</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.799242863632193</v>
+        <v>6.599265132348893</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08047763437039177</v>
+        <v>0.08038777173910701</v>
       </c>
       <c r="C36">
-        <v>113.416891319824</v>
+        <v>111.8886780526215</v>
       </c>
       <c r="D36">
-        <v>161.454891319824</v>
+        <v>161.5936780526215</v>
       </c>
       <c r="E36">
-        <v>24.77800000000001</v>
+        <v>26.44500000000001</v>
       </c>
       <c r="F36">
-        <v>56.67800000000001</v>
+        <v>58.34500000000001</v>
       </c>
       <c r="G36">
         <v>8.640000000000001</v>
@@ -4239,28 +4239,28 @@
         <v>20.31</v>
       </c>
       <c r="M36">
-        <v>3.077615400000001</v>
+        <v>3.168133500000001</v>
       </c>
       <c r="N36">
-        <v>17.2323846</v>
+        <v>17.1418665</v>
       </c>
       <c r="O36">
-        <v>3.274153073999999</v>
+        <v>3.256954635</v>
       </c>
       <c r="P36">
-        <v>13.958231526</v>
+        <v>13.884911865</v>
       </c>
       <c r="Q36">
-        <v>21.848231526</v>
+        <v>21.774911865</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09927790056119964</v>
+        <v>0.09999034113708771</v>
       </c>
       <c r="T36">
-        <v>0.9794665294413121</v>
+        <v>0.992515128787498</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.599265132348893</v>
+        <v>6.410714699996069</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08038777173910701</v>
+        <v>0.08029790910782228</v>
       </c>
       <c r="C37">
-        <v>111.8886780526215</v>
+        <v>110.3607035930351</v>
       </c>
       <c r="D37">
-        <v>161.5936780526215</v>
+        <v>161.7327035930351</v>
       </c>
       <c r="E37">
-        <v>26.44500000000001</v>
+        <v>28.11200000000002</v>
       </c>
       <c r="F37">
-        <v>58.34500000000001</v>
+        <v>60.01200000000001</v>
       </c>
       <c r="G37">
         <v>8.640000000000001</v>
@@ -4321,28 +4321,28 @@
         <v>20.31</v>
       </c>
       <c r="M37">
-        <v>3.168133500000001</v>
+        <v>3.258651600000001</v>
       </c>
       <c r="N37">
-        <v>17.1418665</v>
+        <v>17.0513484</v>
       </c>
       <c r="O37">
-        <v>3.256954635</v>
+        <v>3.239756196</v>
       </c>
       <c r="P37">
-        <v>13.884911865</v>
+        <v>13.811592204</v>
       </c>
       <c r="Q37">
-        <v>21.774911865</v>
+        <v>21.701592204</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09999034113708771</v>
+        <v>0.1007250454809723</v>
       </c>
       <c r="T37">
-        <v>0.992515128787498</v>
+        <v>1.005971496863252</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.410714699996069</v>
+        <v>6.232639291662844</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08029790910782228</v>
+        <v>0.08050774647653755</v>
       </c>
       <c r="C38">
-        <v>110.3607035930351</v>
+        <v>108.3694385276395</v>
       </c>
       <c r="D38">
-        <v>161.7327035930351</v>
+        <v>161.4084385276395</v>
       </c>
       <c r="E38">
-        <v>28.112</v>
+        <v>29.779</v>
       </c>
       <c r="F38">
-        <v>60.012</v>
+        <v>61.679</v>
       </c>
       <c r="G38">
         <v>8.640000000000001</v>
@@ -4403,45 +4403,45 @@
         <v>20.31</v>
       </c>
       <c r="M38">
-        <v>3.2586516</v>
+        <v>3.4108487</v>
       </c>
       <c r="N38">
-        <v>17.0513484</v>
+        <v>16.8991513</v>
       </c>
       <c r="O38">
-        <v>3.239756196</v>
+        <v>3.210838747</v>
       </c>
       <c r="P38">
-        <v>13.811592204</v>
+        <v>13.688312553</v>
       </c>
       <c r="Q38">
-        <v>21.701592204</v>
+        <v>21.578312553</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1007250454809723</v>
+        <v>0.1014830737722818</v>
       </c>
       <c r="T38">
-        <v>1.005971496863252</v>
+        <v>1.019855051227126</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.19</v>
       </c>
       <c r="W38">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.232639291662846</v>
+        <v>5.954529733318279</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08050774647653755</v>
+        <v>0.08042598384525282</v>
       </c>
       <c r="C39">
-        <v>108.3694385276395</v>
+        <v>106.828632901447</v>
       </c>
       <c r="D39">
-        <v>161.4084385276395</v>
+        <v>161.534632901447</v>
       </c>
       <c r="E39">
-        <v>29.779</v>
+        <v>31.44600000000001</v>
       </c>
       <c r="F39">
-        <v>61.679</v>
+        <v>63.34600000000001</v>
       </c>
       <c r="G39">
         <v>8.640000000000001</v>
@@ -4485,28 +4485,28 @@
         <v>20.31</v>
       </c>
       <c r="M39">
-        <v>3.4108487</v>
+        <v>3.503033800000001</v>
       </c>
       <c r="N39">
-        <v>16.8991513</v>
+        <v>16.8069662</v>
       </c>
       <c r="O39">
-        <v>3.210838747</v>
+        <v>3.193323578</v>
       </c>
       <c r="P39">
-        <v>13.688312553</v>
+        <v>13.613642622</v>
       </c>
       <c r="Q39">
-        <v>21.578312553</v>
+        <v>21.503642622</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1014830737722818</v>
+        <v>0.1022655545891174</v>
       </c>
       <c r="T39">
-        <v>1.019855051227126</v>
+        <v>1.034186462183383</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.954529733318279</v>
+        <v>5.797831582441481</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08042598384525282</v>
+        <v>0.08034422121396806</v>
       </c>
       <c r="C40">
-        <v>106.828632901447</v>
+        <v>105.2880247553933</v>
       </c>
       <c r="D40">
-        <v>161.534632901447</v>
+        <v>161.6610247553933</v>
       </c>
       <c r="E40">
-        <v>31.44600000000001</v>
+        <v>33.11300000000001</v>
       </c>
       <c r="F40">
-        <v>63.34600000000001</v>
+        <v>65.01300000000001</v>
       </c>
       <c r="G40">
         <v>8.640000000000001</v>
@@ -4567,28 +4567,28 @@
         <v>20.31</v>
       </c>
       <c r="M40">
-        <v>3.503033800000001</v>
+        <v>3.5952189</v>
       </c>
       <c r="N40">
-        <v>16.8069662</v>
+        <v>16.7147811</v>
       </c>
       <c r="O40">
-        <v>3.193323578</v>
+        <v>3.175808409</v>
       </c>
       <c r="P40">
-        <v>13.613642622</v>
+        <v>13.538972691</v>
       </c>
       <c r="Q40">
-        <v>21.503642622</v>
+        <v>21.428972691</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1022655545891174</v>
+        <v>0.1030736905147017</v>
       </c>
       <c r="T40">
-        <v>1.034186462183383</v>
+        <v>1.048987755466074</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.797831582441481</v>
+        <v>5.649169234173752</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08034422121396806</v>
+        <v>0.08026245858268333</v>
       </c>
       <c r="C41">
-        <v>105.2880247553933</v>
+        <v>103.747614553393</v>
       </c>
       <c r="D41">
-        <v>161.6610247553933</v>
+        <v>161.787614553393</v>
       </c>
       <c r="E41">
-        <v>33.11300000000001</v>
+        <v>34.78000000000001</v>
       </c>
       <c r="F41">
-        <v>65.01300000000001</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="G41">
         <v>8.640000000000001</v>
@@ -4649,28 +4649,28 @@
         <v>20.31</v>
       </c>
       <c r="M41">
-        <v>3.5952189</v>
+        <v>3.687404</v>
       </c>
       <c r="N41">
-        <v>16.7147811</v>
+        <v>16.622596</v>
       </c>
       <c r="O41">
-        <v>3.175808409</v>
+        <v>3.158293239999999</v>
       </c>
       <c r="P41">
-        <v>13.538972691</v>
+        <v>13.46430276</v>
       </c>
       <c r="Q41">
-        <v>21.428972691</v>
+        <v>21.35430276</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1030736905147017</v>
+        <v>0.1039087643044722</v>
       </c>
       <c r="T41">
-        <v>1.048987755466074</v>
+        <v>1.064282425191522</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.649169234173752</v>
+        <v>5.507940003319407</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08026245858268333</v>
+        <v>0.0801806959513986</v>
       </c>
       <c r="C42">
-        <v>103.747614553393</v>
+        <v>102.207402760815</v>
       </c>
       <c r="D42">
-        <v>161.787614553393</v>
+        <v>161.914402760815</v>
       </c>
       <c r="E42">
-        <v>34.78000000000001</v>
+        <v>36.44700000000001</v>
       </c>
       <c r="F42">
-        <v>66.68000000000001</v>
+        <v>68.34700000000001</v>
       </c>
       <c r="G42">
         <v>8.640000000000001</v>
@@ -4731,28 +4731,28 @@
         <v>20.31</v>
       </c>
       <c r="M42">
-        <v>3.687404</v>
+        <v>3.779589100000001</v>
       </c>
       <c r="N42">
-        <v>16.622596</v>
+        <v>16.5304109</v>
       </c>
       <c r="O42">
-        <v>3.158293239999999</v>
+        <v>3.140778071</v>
       </c>
       <c r="P42">
-        <v>13.46430276</v>
+        <v>13.389632829</v>
       </c>
       <c r="Q42">
-        <v>21.35430276</v>
+        <v>21.279632829</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1039087643044722</v>
+        <v>0.1047721456803366</v>
       </c>
       <c r="T42">
-        <v>1.064282425191522</v>
+        <v>1.080095558297493</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.507940003319407</v>
+        <v>5.373600003238447</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0801806959513986</v>
+        <v>0.08009893332011385</v>
       </c>
       <c r="C43">
-        <v>102.207402760815</v>
+        <v>100.667389844488</v>
       </c>
       <c r="D43">
-        <v>161.914402760815</v>
+        <v>162.041389844488</v>
       </c>
       <c r="E43">
-        <v>36.44700000000001</v>
+        <v>38.11400000000001</v>
       </c>
       <c r="F43">
-        <v>68.34700000000001</v>
+        <v>70.01400000000001</v>
       </c>
       <c r="G43">
         <v>8.640000000000001</v>
@@ -4813,28 +4813,28 @@
         <v>20.31</v>
       </c>
       <c r="M43">
-        <v>3.779589100000001</v>
+        <v>3.871774200000001</v>
       </c>
       <c r="N43">
-        <v>16.5304109</v>
+        <v>16.4382258</v>
       </c>
       <c r="O43">
-        <v>3.140778071</v>
+        <v>3.123262902</v>
       </c>
       <c r="P43">
-        <v>13.389632829</v>
+        <v>13.314962898</v>
       </c>
       <c r="Q43">
-        <v>21.279632829</v>
+        <v>21.204962898</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1047721456803366</v>
+        <v>0.1056652988277825</v>
       </c>
       <c r="T43">
-        <v>1.080095558297493</v>
+        <v>1.096453971855395</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.373600003238447</v>
+        <v>5.245657146018483</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08009893332011386</v>
+        <v>0.08001717068882912</v>
       </c>
       <c r="C44">
-        <v>100.667389844488</v>
+        <v>99.12757627270648</v>
       </c>
       <c r="D44">
-        <v>162.041389844488</v>
+        <v>162.1685762727065</v>
       </c>
       <c r="E44">
-        <v>38.11400000000001</v>
+        <v>39.78100000000001</v>
       </c>
       <c r="F44">
-        <v>70.01400000000001</v>
+        <v>71.68100000000001</v>
       </c>
       <c r="G44">
         <v>8.640000000000001</v>
@@ -4895,28 +4895,28 @@
         <v>20.31</v>
       </c>
       <c r="M44">
-        <v>3.871774200000001</v>
+        <v>3.963959300000001</v>
       </c>
       <c r="N44">
-        <v>16.4382258</v>
+        <v>16.3460407</v>
       </c>
       <c r="O44">
-        <v>3.123262902</v>
+        <v>3.105747732999999</v>
       </c>
       <c r="P44">
-        <v>13.314962898</v>
+        <v>13.240292967</v>
       </c>
       <c r="Q44">
-        <v>21.204962898</v>
+        <v>21.130292967</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1056652988277825</v>
+        <v>0.1065897906821563</v>
       </c>
       <c r="T44">
-        <v>1.096453971855394</v>
+        <v>1.11338636483638</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.245657146018483</v>
+        <v>5.12366511936689</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08001717068882912</v>
+        <v>0.07993540805754439</v>
       </c>
       <c r="C45">
-        <v>99.12757627270648</v>
+        <v>97.58796251523626</v>
       </c>
       <c r="D45">
-        <v>162.1685762727065</v>
+        <v>162.2959625152363</v>
       </c>
       <c r="E45">
-        <v>39.78100000000001</v>
+        <v>41.44800000000001</v>
       </c>
       <c r="F45">
-        <v>71.68100000000001</v>
+        <v>73.34800000000001</v>
       </c>
       <c r="G45">
         <v>8.640000000000001</v>
@@ -4977,28 +4977,28 @@
         <v>20.31</v>
       </c>
       <c r="M45">
-        <v>3.963959300000001</v>
+        <v>4.056144400000001</v>
       </c>
       <c r="N45">
-        <v>16.3460407</v>
+        <v>16.2538556</v>
       </c>
       <c r="O45">
-        <v>3.105747732999999</v>
+        <v>3.088232564</v>
       </c>
       <c r="P45">
-        <v>13.240292967</v>
+        <v>13.165623036</v>
       </c>
       <c r="Q45">
-        <v>21.130292967</v>
+        <v>21.055623036</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1065897906821563</v>
+        <v>0.1075473001027578</v>
       </c>
       <c r="T45">
-        <v>1.11338636483638</v>
+        <v>1.130923486138115</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.12366511936689</v>
+        <v>5.007218184835825</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07993540805754439</v>
+        <v>0.07985364542625964</v>
       </c>
       <c r="C46">
-        <v>97.58796251523626</v>
+        <v>96.04854904332038</v>
       </c>
       <c r="D46">
-        <v>162.2959625152363</v>
+        <v>162.4235490433204</v>
       </c>
       <c r="E46">
-        <v>41.44800000000001</v>
+        <v>43.11500000000002</v>
       </c>
       <c r="F46">
-        <v>73.34800000000001</v>
+        <v>75.01500000000001</v>
       </c>
       <c r="G46">
         <v>8.640000000000001</v>
@@ -5059,28 +5059,28 @@
         <v>20.31</v>
       </c>
       <c r="M46">
-        <v>4.056144400000001</v>
+        <v>4.148329500000001</v>
       </c>
       <c r="N46">
-        <v>16.2538556</v>
+        <v>16.1616705</v>
       </c>
       <c r="O46">
-        <v>3.088232564</v>
+        <v>3.070717395</v>
       </c>
       <c r="P46">
-        <v>13.165623036</v>
+        <v>13.090953105</v>
       </c>
       <c r="Q46">
-        <v>21.055623036</v>
+        <v>20.980953105</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1075473001027578</v>
+        <v>0.1085396280477448</v>
       </c>
       <c r="T46">
-        <v>1.130923486138115</v>
+        <v>1.149098320941731</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.007218184835825</v>
+        <v>4.895946669617251</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07985364542625964</v>
+        <v>0.07977188279497491</v>
       </c>
       <c r="C47">
-        <v>96.04854904332038</v>
+        <v>94.50933632968486</v>
       </c>
       <c r="D47">
-        <v>162.4235490433204</v>
+        <v>162.5513363296849</v>
       </c>
       <c r="E47">
-        <v>43.11500000000002</v>
+        <v>44.78200000000002</v>
       </c>
       <c r="F47">
-        <v>75.01500000000001</v>
+        <v>76.68200000000002</v>
       </c>
       <c r="G47">
         <v>8.640000000000001</v>
@@ -5141,28 +5141,28 @@
         <v>20.31</v>
       </c>
       <c r="M47">
-        <v>4.148329500000001</v>
+        <v>4.240514600000001</v>
       </c>
       <c r="N47">
-        <v>16.1616705</v>
+        <v>16.0694854</v>
       </c>
       <c r="O47">
-        <v>3.070717395</v>
+        <v>3.053202226</v>
       </c>
       <c r="P47">
-        <v>13.090953105</v>
+        <v>13.016283174</v>
       </c>
       <c r="Q47">
-        <v>20.980953105</v>
+        <v>20.906283174</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1085396280477448</v>
+        <v>0.1095687088795831</v>
       </c>
       <c r="T47">
-        <v>1.149098320941731</v>
+        <v>1.167946297775111</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.895946669617251</v>
+        <v>4.789513046364702</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07977188279497491</v>
+        <v>0.07969012016369016</v>
       </c>
       <c r="C48">
-        <v>94.50933632968486</v>
+        <v>92.97032484854466</v>
       </c>
       <c r="D48">
-        <v>162.5513363296849</v>
+        <v>162.6793248485447</v>
       </c>
       <c r="E48">
-        <v>44.78200000000002</v>
+        <v>46.44900000000002</v>
       </c>
       <c r="F48">
-        <v>76.68200000000002</v>
+        <v>78.34900000000002</v>
       </c>
       <c r="G48">
         <v>8.640000000000001</v>
@@ -5223,28 +5223,28 @@
         <v>20.31</v>
       </c>
       <c r="M48">
-        <v>4.240514600000001</v>
+        <v>4.332699700000001</v>
       </c>
       <c r="N48">
-        <v>16.0694854</v>
+        <v>15.9773003</v>
       </c>
       <c r="O48">
-        <v>3.053202226</v>
+        <v>3.035687057</v>
       </c>
       <c r="P48">
-        <v>13.016283174</v>
+        <v>12.941613243</v>
       </c>
       <c r="Q48">
-        <v>20.906283174</v>
+        <v>20.831613243</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1095687088795831</v>
+        <v>0.1106366229503588</v>
       </c>
       <c r="T48">
-        <v>1.167946297775111</v>
+        <v>1.187505519017298</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.789513046364702</v>
+        <v>4.687608513463325</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07969012016369016</v>
+        <v>0.07960835753240543</v>
       </c>
       <c r="C49">
-        <v>92.97032484854466</v>
+        <v>91.43151507560935</v>
       </c>
       <c r="D49">
-        <v>162.6793248485447</v>
+        <v>162.8075150756094</v>
       </c>
       <c r="E49">
-        <v>46.44900000000002</v>
+        <v>48.11600000000002</v>
       </c>
       <c r="F49">
-        <v>78.34900000000002</v>
+        <v>80.01600000000002</v>
       </c>
       <c r="G49">
         <v>8.640000000000001</v>
@@ -5305,28 +5305,28 @@
         <v>20.31</v>
       </c>
       <c r="M49">
-        <v>4.332699700000001</v>
+        <v>4.424884800000001</v>
       </c>
       <c r="N49">
-        <v>15.9773003</v>
+        <v>15.8851152</v>
       </c>
       <c r="O49">
-        <v>3.035687057</v>
+        <v>3.018171887999999</v>
       </c>
       <c r="P49">
-        <v>12.941613243</v>
+        <v>12.866943312</v>
       </c>
       <c r="Q49">
-        <v>20.831613243</v>
+        <v>20.756943312</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1106366229503588</v>
+        <v>0.1117456106392412</v>
       </c>
       <c r="T49">
-        <v>1.187505519017298</v>
+        <v>1.207817017999569</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.687608513463325</v>
+        <v>4.589950002766173</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07960835753240542</v>
+        <v>0.08051884490112068</v>
       </c>
       <c r="C50">
-        <v>91.43151507560937</v>
+        <v>88.34832415418735</v>
       </c>
       <c r="D50">
-        <v>162.8075150756094</v>
+        <v>161.3913241541873</v>
       </c>
       <c r="E50">
-        <v>48.11600000000001</v>
+        <v>49.78300000000001</v>
       </c>
       <c r="F50">
-        <v>80.01600000000001</v>
+        <v>81.68300000000001</v>
       </c>
       <c r="G50">
         <v>8.640000000000001</v>
@@ -5387,45 +5387,45 @@
         <v>20.31</v>
       </c>
       <c r="M50">
-        <v>4.4248848</v>
+        <v>4.721277400000001</v>
       </c>
       <c r="N50">
-        <v>15.8851152</v>
+        <v>15.5887226</v>
       </c>
       <c r="O50">
-        <v>3.018171887999999</v>
+        <v>2.961857294</v>
       </c>
       <c r="P50">
-        <v>12.866943312</v>
+        <v>12.626865306</v>
       </c>
       <c r="Q50">
-        <v>20.756943312</v>
+        <v>20.516865306</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1117456106392412</v>
+        <v>0.1128980880414131</v>
       </c>
       <c r="T50">
-        <v>1.207817017999569</v>
+        <v>1.228925046353694</v>
       </c>
       <c r="U50">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.19</v>
       </c>
       <c r="W50">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.589950002766173</v>
+        <v>4.301801880990936</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08051884490112068</v>
+        <v>0.08045733226983594</v>
       </c>
       <c r="C51">
-        <v>88.34832415418735</v>
+        <v>86.77622568594468</v>
       </c>
       <c r="D51">
-        <v>161.3913241541873</v>
+        <v>161.4862256859447</v>
       </c>
       <c r="E51">
-        <v>49.78300000000001</v>
+        <v>51.45000000000001</v>
       </c>
       <c r="F51">
-        <v>81.68300000000001</v>
+        <v>83.35000000000001</v>
       </c>
       <c r="G51">
         <v>8.640000000000001</v>
@@ -5469,28 +5469,28 @@
         <v>20.31</v>
       </c>
       <c r="M51">
-        <v>4.721277400000001</v>
+        <v>4.817630000000001</v>
       </c>
       <c r="N51">
-        <v>15.5887226</v>
+        <v>15.49237</v>
       </c>
       <c r="O51">
-        <v>2.961857294</v>
+        <v>2.9435503</v>
       </c>
       <c r="P51">
-        <v>12.626865306</v>
+        <v>12.5488197</v>
       </c>
       <c r="Q51">
-        <v>20.516865306</v>
+        <v>20.4388197</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1128980880414131</v>
+        <v>0.1140966645396719</v>
       </c>
       <c r="T51">
-        <v>1.228925046353694</v>
+        <v>1.250877395841983</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.301801880990936</v>
+        <v>4.215765843371116</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08045733226983594</v>
+        <v>0.08039581963855122</v>
       </c>
       <c r="C52">
-        <v>86.77622568594468</v>
+        <v>85.20423889160746</v>
       </c>
       <c r="D52">
-        <v>161.4862256859447</v>
+        <v>161.5812388916075</v>
       </c>
       <c r="E52">
-        <v>51.45000000000001</v>
+        <v>53.11700000000001</v>
       </c>
       <c r="F52">
-        <v>83.35000000000001</v>
+        <v>85.01700000000001</v>
       </c>
       <c r="G52">
         <v>8.640000000000001</v>
@@ -5551,28 +5551,28 @@
         <v>20.31</v>
       </c>
       <c r="M52">
-        <v>4.817630000000001</v>
+        <v>4.913982600000001</v>
       </c>
       <c r="N52">
-        <v>15.49237</v>
+        <v>15.3960174</v>
       </c>
       <c r="O52">
-        <v>2.9435503</v>
+        <v>2.925243306</v>
       </c>
       <c r="P52">
-        <v>12.5488197</v>
+        <v>12.470774094</v>
       </c>
       <c r="Q52">
-        <v>20.4388197</v>
+        <v>20.360774094</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1140966645396719</v>
+        <v>0.1153441625276555</v>
       </c>
       <c r="T52">
-        <v>1.250877395841983</v>
+        <v>1.273725759595101</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.215765843371116</v>
+        <v>4.1331037680109</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08039581963855122</v>
+        <v>0.08033430700726647</v>
       </c>
       <c r="C53">
-        <v>85.20423889160746</v>
+        <v>83.63236396840774</v>
       </c>
       <c r="D53">
-        <v>161.5812388916075</v>
+        <v>161.6763639684077</v>
       </c>
       <c r="E53">
-        <v>53.11700000000001</v>
+        <v>54.78400000000001</v>
       </c>
       <c r="F53">
-        <v>85.01700000000001</v>
+        <v>86.68400000000001</v>
       </c>
       <c r="G53">
         <v>8.640000000000001</v>
@@ -5633,28 +5633,28 @@
         <v>20.31</v>
       </c>
       <c r="M53">
-        <v>4.913982600000001</v>
+        <v>5.010335200000001</v>
       </c>
       <c r="N53">
-        <v>15.3960174</v>
+        <v>15.2996648</v>
       </c>
       <c r="O53">
-        <v>2.925243306</v>
+        <v>2.906936312</v>
       </c>
       <c r="P53">
-        <v>12.470774094</v>
+        <v>12.392728488</v>
       </c>
       <c r="Q53">
-        <v>20.360774094</v>
+        <v>20.282728488</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1153441625276555</v>
+        <v>0.1166436395984718</v>
       </c>
       <c r="T53">
-        <v>1.273725759595101</v>
+        <v>1.297526138504599</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.1331037680109</v>
+        <v>4.053621003241458</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08033430700726647</v>
+        <v>0.08177534437598173</v>
       </c>
       <c r="C54">
-        <v>83.63236396840774</v>
+        <v>79.76592019170293</v>
       </c>
       <c r="D54">
-        <v>161.6763639684077</v>
+        <v>159.4769201917029</v>
       </c>
       <c r="E54">
-        <v>54.78400000000001</v>
+        <v>56.45100000000001</v>
       </c>
       <c r="F54">
-        <v>86.68400000000001</v>
+        <v>88.35100000000001</v>
       </c>
       <c r="G54">
         <v>8.640000000000001</v>
@@ -5715,45 +5715,45 @@
         <v>20.31</v>
       </c>
       <c r="M54">
-        <v>5.010335200000001</v>
+        <v>5.415916300000001</v>
       </c>
       <c r="N54">
-        <v>15.2996648</v>
+        <v>14.8940837</v>
       </c>
       <c r="O54">
-        <v>2.906936312</v>
+        <v>2.829875903</v>
       </c>
       <c r="P54">
-        <v>12.392728488</v>
+        <v>12.064207797</v>
       </c>
       <c r="Q54">
-        <v>20.282728488</v>
+        <v>19.954207797</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1166436395984718</v>
+        <v>0.1179984135659186</v>
       </c>
       <c r="T54">
-        <v>1.297526138504599</v>
+        <v>1.322339299495352</v>
       </c>
       <c r="U54">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.19</v>
       </c>
       <c r="W54">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.053621003241458</v>
+        <v>3.750057954182194</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08177534437598173</v>
+        <v>0.081742181744697</v>
       </c>
       <c r="C55">
-        <v>79.76592019170293</v>
+        <v>78.14886310772944</v>
       </c>
       <c r="D55">
-        <v>159.4769201917029</v>
+        <v>159.5268631077294</v>
       </c>
       <c r="E55">
-        <v>56.45100000000001</v>
+        <v>58.11800000000002</v>
       </c>
       <c r="F55">
-        <v>88.35100000000001</v>
+        <v>90.01800000000001</v>
       </c>
       <c r="G55">
         <v>8.640000000000001</v>
@@ -5797,28 +5797,28 @@
         <v>20.31</v>
       </c>
       <c r="M55">
-        <v>5.415916300000001</v>
+        <v>5.518103400000001</v>
       </c>
       <c r="N55">
-        <v>14.8940837</v>
+        <v>14.7918966</v>
       </c>
       <c r="O55">
-        <v>2.829875903</v>
+        <v>2.810460353999999</v>
       </c>
       <c r="P55">
-        <v>12.064207797</v>
+        <v>11.981436246</v>
       </c>
       <c r="Q55">
-        <v>19.954207797</v>
+        <v>19.871436246</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1179984135659186</v>
+        <v>0.1194120907493413</v>
       </c>
       <c r="T55">
-        <v>1.322339299495352</v>
+        <v>1.348231293572659</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.750057954182194</v>
+        <v>3.680612436512153</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.081742181744697</v>
+        <v>0.08170901911341225</v>
       </c>
       <c r="C56">
-        <v>78.14886310772944</v>
+        <v>76.53183731450621</v>
       </c>
       <c r="D56">
-        <v>159.5268631077294</v>
+        <v>159.5768373145062</v>
       </c>
       <c r="E56">
-        <v>58.11800000000002</v>
+        <v>59.78500000000002</v>
       </c>
       <c r="F56">
-        <v>90.01800000000001</v>
+        <v>91.68500000000002</v>
       </c>
       <c r="G56">
         <v>8.640000000000001</v>
@@ -5879,28 +5879,28 @@
         <v>20.31</v>
       </c>
       <c r="M56">
-        <v>5.518103400000001</v>
+        <v>5.620290500000001</v>
       </c>
       <c r="N56">
-        <v>14.7918966</v>
+        <v>14.6897095</v>
       </c>
       <c r="O56">
-        <v>2.810460353999999</v>
+        <v>2.791044804999999</v>
       </c>
       <c r="P56">
-        <v>11.981436246</v>
+        <v>11.898664695</v>
       </c>
       <c r="Q56">
-        <v>19.871436246</v>
+        <v>19.788664695</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1194120907493413</v>
+        <v>0.120888598029805</v>
       </c>
       <c r="T56">
-        <v>1.348231293572659</v>
+        <v>1.375274042942291</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.680612436512153</v>
+        <v>3.61369221039375</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08170901911341225</v>
+        <v>0.08167585648212751</v>
       </c>
       <c r="C57">
-        <v>76.53183731450621</v>
+        <v>74.9148428414493</v>
       </c>
       <c r="D57">
-        <v>159.5768373145062</v>
+        <v>159.6268428414493</v>
       </c>
       <c r="E57">
-        <v>59.78500000000002</v>
+        <v>61.45200000000002</v>
       </c>
       <c r="F57">
-        <v>91.68500000000002</v>
+        <v>93.35200000000002</v>
       </c>
       <c r="G57">
         <v>8.640000000000001</v>
@@ -5961,28 +5961,28 @@
         <v>20.31</v>
       </c>
       <c r="M57">
-        <v>5.620290500000001</v>
+        <v>5.722477600000001</v>
       </c>
       <c r="N57">
-        <v>14.6897095</v>
+        <v>14.5875224</v>
       </c>
       <c r="O57">
-        <v>2.791044804999999</v>
+        <v>2.771629256</v>
       </c>
       <c r="P57">
-        <v>11.898664695</v>
+        <v>11.815893144</v>
       </c>
       <c r="Q57">
-        <v>19.788664695</v>
+        <v>19.705893144</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.120888598029805</v>
+        <v>0.1224322192775625</v>
       </c>
       <c r="T57">
-        <v>1.375274042942291</v>
+        <v>1.403546008192361</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.61369221039375</v>
+        <v>3.549161992351004</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08167585648212751</v>
+        <v>0.08293545385084278</v>
       </c>
       <c r="C58">
-        <v>74.9148428414493</v>
+        <v>71.3702636743232</v>
       </c>
       <c r="D58">
-        <v>159.6268428414493</v>
+        <v>157.7492636743232</v>
       </c>
       <c r="E58">
-        <v>61.45200000000002</v>
+        <v>63.11900000000002</v>
       </c>
       <c r="F58">
-        <v>93.35200000000002</v>
+        <v>95.01900000000002</v>
       </c>
       <c r="G58">
         <v>8.640000000000001</v>
@@ -6043,45 +6043,45 @@
         <v>20.31</v>
       </c>
       <c r="M58">
-        <v>5.722477600000001</v>
+        <v>6.090717900000001</v>
       </c>
       <c r="N58">
-        <v>14.5875224</v>
+        <v>14.2192821</v>
       </c>
       <c r="O58">
-        <v>2.771629256</v>
+        <v>2.701663599</v>
       </c>
       <c r="P58">
-        <v>11.815893144</v>
+        <v>11.517618501</v>
       </c>
       <c r="Q58">
-        <v>19.705893144</v>
+        <v>19.407618501</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1224322192775625</v>
+        <v>0.1240476368624251</v>
       </c>
       <c r="T58">
-        <v>1.403546008192361</v>
+        <v>1.433132948570341</v>
       </c>
       <c r="U58">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.19</v>
       </c>
       <c r="W58">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.549161992351004</v>
+        <v>3.334582282985064</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08293545385084278</v>
+        <v>0.08292497121955805</v>
       </c>
       <c r="C59">
-        <v>71.3702636743232</v>
+        <v>69.71870699730808</v>
       </c>
       <c r="D59">
-        <v>157.7492636743232</v>
+        <v>157.7647069973081</v>
       </c>
       <c r="E59">
-        <v>63.11900000000002</v>
+        <v>64.78600000000003</v>
       </c>
       <c r="F59">
-        <v>95.01900000000002</v>
+        <v>96.68600000000002</v>
       </c>
       <c r="G59">
         <v>8.640000000000001</v>
@@ -6125,28 +6125,28 @@
         <v>20.31</v>
       </c>
       <c r="M59">
-        <v>6.090717900000001</v>
+        <v>6.197572600000002</v>
       </c>
       <c r="N59">
-        <v>14.2192821</v>
+        <v>14.1124274</v>
       </c>
       <c r="O59">
-        <v>2.701663599</v>
+        <v>2.681361206</v>
       </c>
       <c r="P59">
-        <v>11.517618501</v>
+        <v>11.431066194</v>
       </c>
       <c r="Q59">
-        <v>19.407618501</v>
+        <v>19.321066194</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1240476368624251</v>
+        <v>0.1257399790941858</v>
       </c>
       <c r="T59">
-        <v>1.433132948570341</v>
+        <v>1.464128790871083</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.334582282985064</v>
+        <v>3.277089485002563</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08292497121955802</v>
+        <v>0.0829144885882733</v>
       </c>
       <c r="C60">
-        <v>69.71870699730815</v>
+        <v>68.0671533443271</v>
       </c>
       <c r="D60">
-        <v>157.7647069973082</v>
+        <v>157.7801533443271</v>
       </c>
       <c r="E60">
-        <v>64.786</v>
+        <v>66.453</v>
       </c>
       <c r="F60">
-        <v>96.68600000000001</v>
+        <v>98.35300000000001</v>
       </c>
       <c r="G60">
         <v>8.640000000000001</v>
@@ -6207,28 +6207,28 @@
         <v>20.31</v>
       </c>
       <c r="M60">
-        <v>6.197572600000001</v>
+        <v>6.304427300000001</v>
       </c>
       <c r="N60">
-        <v>14.1124274</v>
+        <v>14.0055727</v>
       </c>
       <c r="O60">
-        <v>2.681361206</v>
+        <v>2.661058813</v>
       </c>
       <c r="P60">
-        <v>11.431066194</v>
+        <v>11.344513887</v>
       </c>
       <c r="Q60">
-        <v>19.321066194</v>
+        <v>19.234513887</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1257399790941858</v>
+        <v>0.1275148746055446</v>
       </c>
       <c r="T60">
-        <v>1.464128790871082</v>
+        <v>1.496636625479177</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.277089485002563</v>
+        <v>3.221545595426248</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0829144885882733</v>
+        <v>0.08290400595698855</v>
       </c>
       <c r="C61">
-        <v>68.0671533443271</v>
+        <v>66.41560271626852</v>
       </c>
       <c r="D61">
-        <v>157.7801533443271</v>
+        <v>157.7956027162685</v>
       </c>
       <c r="E61">
-        <v>66.453</v>
+        <v>68.12</v>
       </c>
       <c r="F61">
-        <v>98.35300000000001</v>
+        <v>100.02</v>
       </c>
       <c r="G61">
         <v>8.640000000000001</v>
@@ -6289,28 +6289,28 @@
         <v>20.31</v>
       </c>
       <c r="M61">
-        <v>6.304427300000001</v>
+        <v>6.411282000000001</v>
       </c>
       <c r="N61">
-        <v>14.0055727</v>
+        <v>13.898718</v>
       </c>
       <c r="O61">
-        <v>2.661058813</v>
+        <v>2.64075642</v>
       </c>
       <c r="P61">
-        <v>11.344513887</v>
+        <v>11.25796158</v>
       </c>
       <c r="Q61">
-        <v>19.234513887</v>
+        <v>19.14796158</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1275148746055446</v>
+        <v>0.1293785148924714</v>
       </c>
       <c r="T61">
-        <v>1.496636625479177</v>
+        <v>1.530769851817676</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.221545595426248</v>
+        <v>3.167853168835811</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08290400595698855</v>
+        <v>0.08289352332570382</v>
       </c>
       <c r="C62">
-        <v>66.41560271626852</v>
+        <v>64.76405511402101</v>
       </c>
       <c r="D62">
-        <v>157.7956027162685</v>
+        <v>157.811055114021</v>
       </c>
       <c r="E62">
-        <v>68.12</v>
+        <v>69.78700000000001</v>
       </c>
       <c r="F62">
-        <v>100.02</v>
+        <v>101.687</v>
       </c>
       <c r="G62">
         <v>8.640000000000001</v>
@@ -6371,28 +6371,28 @@
         <v>20.31</v>
       </c>
       <c r="M62">
-        <v>6.411282000000001</v>
+        <v>6.518136700000001</v>
       </c>
       <c r="N62">
-        <v>13.898718</v>
+        <v>13.7918633</v>
       </c>
       <c r="O62">
-        <v>2.64075642</v>
+        <v>2.620454027</v>
       </c>
       <c r="P62">
-        <v>11.25796158</v>
+        <v>11.171409273</v>
       </c>
       <c r="Q62">
-        <v>19.14796158</v>
+        <v>19.061409273</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1293785148924714</v>
+        <v>0.1313377264761637</v>
       </c>
       <c r="T62">
-        <v>1.530769851817676</v>
+        <v>1.566653500019688</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.167853168835811</v>
+        <v>3.115921149674568</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08289352332570382</v>
+        <v>0.0828830406944191</v>
       </c>
       <c r="C63">
-        <v>64.76405511402101</v>
+        <v>63.11251053847351</v>
       </c>
       <c r="D63">
-        <v>157.811055114021</v>
+        <v>157.8265105384735</v>
       </c>
       <c r="E63">
-        <v>69.78700000000001</v>
+        <v>71.45400000000001</v>
       </c>
       <c r="F63">
-        <v>101.687</v>
+        <v>103.354</v>
       </c>
       <c r="G63">
         <v>8.640000000000001</v>
@@ -6453,28 +6453,28 @@
         <v>20.31</v>
       </c>
       <c r="M63">
-        <v>6.518136700000001</v>
+        <v>6.624991400000002</v>
       </c>
       <c r="N63">
-        <v>13.7918633</v>
+        <v>13.6850086</v>
       </c>
       <c r="O63">
-        <v>2.620454027</v>
+        <v>2.600151633999999</v>
       </c>
       <c r="P63">
-        <v>11.171409273</v>
+        <v>11.084856966</v>
       </c>
       <c r="Q63">
-        <v>19.061409273</v>
+        <v>18.974856966</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1313377264761637</v>
+        <v>0.1334000544589976</v>
       </c>
       <c r="T63">
-        <v>1.566653500019688</v>
+        <v>1.604425761284963</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.115921149674568</v>
+        <v>3.065664356937881</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0828830406944191</v>
+        <v>0.08287255806313434</v>
       </c>
       <c r="C64">
-        <v>63.11251053847351</v>
+        <v>61.46096899051548</v>
       </c>
       <c r="D64">
-        <v>157.8265105384735</v>
+        <v>157.8419689905155</v>
       </c>
       <c r="E64">
-        <v>71.45400000000001</v>
+        <v>73.12100000000001</v>
       </c>
       <c r="F64">
-        <v>103.354</v>
+        <v>105.021</v>
       </c>
       <c r="G64">
         <v>8.640000000000001</v>
@@ -6535,28 +6535,28 @@
         <v>20.31</v>
       </c>
       <c r="M64">
-        <v>6.624991400000002</v>
+        <v>6.731846100000001</v>
       </c>
       <c r="N64">
-        <v>13.6850086</v>
+        <v>13.5781539</v>
       </c>
       <c r="O64">
-        <v>2.600151633999999</v>
+        <v>2.579849240999999</v>
       </c>
       <c r="P64">
-        <v>11.084856966</v>
+        <v>10.998304659</v>
       </c>
       <c r="Q64">
-        <v>18.974856966</v>
+        <v>18.888304659</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1334000544589976</v>
+        <v>0.1355738596300928</v>
       </c>
       <c r="T64">
-        <v>1.604425761284963</v>
+        <v>1.644239766402416</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.065664356937881</v>
+        <v>3.017003017938867</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08287255806313434</v>
+        <v>0.08690559543184961</v>
       </c>
       <c r="C65">
-        <v>61.46096899051548</v>
+        <v>54.06197560128115</v>
       </c>
       <c r="D65">
-        <v>157.8419689905155</v>
+        <v>152.1099756012812</v>
       </c>
       <c r="E65">
-        <v>73.12100000000001</v>
+        <v>74.78800000000001</v>
       </c>
       <c r="F65">
-        <v>105.021</v>
+        <v>106.688</v>
       </c>
       <c r="G65">
         <v>8.640000000000001</v>
@@ -6617,45 +6617,45 @@
         <v>20.31</v>
       </c>
       <c r="M65">
-        <v>6.731846100000001</v>
+        <v>7.670867200000002</v>
       </c>
       <c r="N65">
-        <v>13.5781539</v>
+        <v>12.6391328</v>
       </c>
       <c r="O65">
-        <v>2.579849240999999</v>
+        <v>2.401435231999999</v>
       </c>
       <c r="P65">
-        <v>10.998304659</v>
+        <v>10.237697568</v>
       </c>
       <c r="Q65">
-        <v>18.888304659</v>
+        <v>18.127697568</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1355738596300928</v>
+        <v>0.1378684317551378</v>
       </c>
       <c r="T65">
-        <v>1.644239766402416</v>
+        <v>1.686265660693061</v>
       </c>
       <c r="U65">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.19</v>
       </c>
       <c r="W65">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.017003017938867</v>
+        <v>2.647679782541405</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08690559543184961</v>
+        <v>0.08695829280056486</v>
       </c>
       <c r="C66">
-        <v>54.06197560128115</v>
+        <v>52.32283304173552</v>
       </c>
       <c r="D66">
-        <v>152.1099756012812</v>
+        <v>152.0378330417355</v>
       </c>
       <c r="E66">
-        <v>74.78800000000001</v>
+        <v>76.45500000000001</v>
       </c>
       <c r="F66">
-        <v>106.688</v>
+        <v>108.355</v>
       </c>
       <c r="G66">
         <v>8.640000000000001</v>
@@ -6699,28 +6699,28 @@
         <v>20.31</v>
       </c>
       <c r="M66">
-        <v>7.670867200000002</v>
+        <v>7.790724500000002</v>
       </c>
       <c r="N66">
-        <v>12.6391328</v>
+        <v>12.5192755</v>
       </c>
       <c r="O66">
-        <v>2.401435231999999</v>
+        <v>2.378662344999999</v>
       </c>
       <c r="P66">
-        <v>10.237697568</v>
+        <v>10.140613155</v>
       </c>
       <c r="Q66">
-        <v>18.127697568</v>
+        <v>18.030613155</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1378684317551378</v>
+        <v>0.1402941222873282</v>
       </c>
       <c r="T66">
-        <v>1.686265660693061</v>
+        <v>1.730693034657456</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.647679782541405</v>
+        <v>2.606946247425383</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08695829280056486</v>
+        <v>0.08701099016928013</v>
       </c>
       <c r="C67">
-        <v>52.32283304173552</v>
+        <v>50.5837588811444</v>
       </c>
       <c r="D67">
-        <v>152.0378330417355</v>
+        <v>151.9657588811444</v>
       </c>
       <c r="E67">
-        <v>76.45500000000001</v>
+        <v>78.12200000000001</v>
       </c>
       <c r="F67">
-        <v>108.355</v>
+        <v>110.022</v>
       </c>
       <c r="G67">
         <v>8.640000000000001</v>
@@ -6781,28 +6781,28 @@
         <v>20.31</v>
       </c>
       <c r="M67">
-        <v>7.790724500000002</v>
+        <v>7.910581800000002</v>
       </c>
       <c r="N67">
-        <v>12.5192755</v>
+        <v>12.3994182</v>
       </c>
       <c r="O67">
-        <v>2.378662344999999</v>
+        <v>2.355889457999999</v>
       </c>
       <c r="P67">
-        <v>10.140613155</v>
+        <v>10.043528742</v>
       </c>
       <c r="Q67">
-        <v>18.030613155</v>
+        <v>17.933528742</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1402941222873282</v>
+        <v>0.1428625004978827</v>
       </c>
       <c r="T67">
-        <v>1.730693034657456</v>
+        <v>1.777733783560934</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.606946247425383</v>
+        <v>2.567447061858331</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08701099016928013</v>
+        <v>0.0870636875379954</v>
       </c>
       <c r="C68">
-        <v>50.5837588811444</v>
+        <v>48.84475302227969</v>
       </c>
       <c r="D68">
-        <v>151.9657588811444</v>
+        <v>151.8937530222797</v>
       </c>
       <c r="E68">
-        <v>78.12200000000001</v>
+        <v>79.78900000000002</v>
       </c>
       <c r="F68">
-        <v>110.022</v>
+        <v>111.689</v>
       </c>
       <c r="G68">
         <v>8.640000000000001</v>
@@ -6863,28 +6863,28 @@
         <v>20.31</v>
       </c>
       <c r="M68">
-        <v>7.910581800000002</v>
+        <v>8.030439100000002</v>
       </c>
       <c r="N68">
-        <v>12.3994182</v>
+        <v>12.2795609</v>
       </c>
       <c r="O68">
-        <v>2.355889457999999</v>
+        <v>2.333116570999999</v>
       </c>
       <c r="P68">
-        <v>10.043528742</v>
+        <v>9.946444328999997</v>
       </c>
       <c r="Q68">
-        <v>17.933528742</v>
+        <v>17.836444329</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1428625004978827</v>
+        <v>0.1455865379939254</v>
       </c>
       <c r="T68">
-        <v>1.777733783560934</v>
+        <v>1.82762548694341</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.567447061858331</v>
+        <v>2.529126956457461</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0870636875379954</v>
+        <v>0.08926450490671065</v>
       </c>
       <c r="C69">
-        <v>48.84475302227969</v>
+        <v>44.23030004384171</v>
       </c>
       <c r="D69">
-        <v>151.8937530222797</v>
+        <v>148.9463000438417</v>
       </c>
       <c r="E69">
-        <v>79.78900000000002</v>
+        <v>81.45600000000002</v>
       </c>
       <c r="F69">
-        <v>111.689</v>
+        <v>113.356</v>
       </c>
       <c r="G69">
         <v>8.640000000000001</v>
@@ -6945,45 +6945,45 @@
         <v>20.31</v>
       </c>
       <c r="M69">
-        <v>8.030439100000002</v>
+        <v>8.592384800000003</v>
       </c>
       <c r="N69">
-        <v>12.2795609</v>
+        <v>11.7176152</v>
       </c>
       <c r="O69">
-        <v>2.333116570999999</v>
+        <v>2.226346887999999</v>
       </c>
       <c r="P69">
-        <v>9.946444328999997</v>
+        <v>9.491268311999995</v>
       </c>
       <c r="Q69">
-        <v>17.836444329</v>
+        <v>17.381268312</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1455865379939254</v>
+        <v>0.1484808278334708</v>
       </c>
       <c r="T69">
-        <v>1.82762548694341</v>
+        <v>1.880635421787292</v>
       </c>
       <c r="U69">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V69">
         <v>0.19</v>
       </c>
       <c r="W69">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.529126956457461</v>
+        <v>2.363720954396734</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08926450490671065</v>
+        <v>0.08934879227542591</v>
       </c>
       <c r="C70">
-        <v>44.23030004384171</v>
+        <v>42.45269051290353</v>
       </c>
       <c r="D70">
-        <v>148.9463000438417</v>
+        <v>148.8356905129036</v>
       </c>
       <c r="E70">
-        <v>81.45600000000002</v>
+        <v>83.12300000000002</v>
       </c>
       <c r="F70">
-        <v>113.356</v>
+        <v>115.023</v>
       </c>
       <c r="G70">
         <v>8.640000000000001</v>
@@ -7027,28 +7027,28 @@
         <v>20.31</v>
       </c>
       <c r="M70">
-        <v>8.592384800000003</v>
+        <v>8.718743400000003</v>
       </c>
       <c r="N70">
-        <v>11.7176152</v>
+        <v>11.5912566</v>
       </c>
       <c r="O70">
-        <v>2.226346887999999</v>
+        <v>2.202338753999999</v>
       </c>
       <c r="P70">
-        <v>9.491268311999995</v>
+        <v>9.388917845999996</v>
       </c>
       <c r="Q70">
-        <v>17.381268312</v>
+        <v>17.278917846</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1484808278334708</v>
+        <v>0.151561846049761</v>
       </c>
       <c r="T70">
-        <v>1.880635421787292</v>
+        <v>1.937065352427552</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.363720954396734</v>
+        <v>2.329464128970694</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08934879227542591</v>
+        <v>0.08943307964414118</v>
       </c>
       <c r="C71">
-        <v>42.45269051290353</v>
+        <v>40.67524514031768</v>
       </c>
       <c r="D71">
-        <v>148.8356905129036</v>
+        <v>148.7252451403177</v>
       </c>
       <c r="E71">
-        <v>83.12300000000002</v>
+        <v>84.79000000000002</v>
       </c>
       <c r="F71">
-        <v>115.023</v>
+        <v>116.69</v>
       </c>
       <c r="G71">
         <v>8.640000000000001</v>
@@ -7109,28 +7109,28 @@
         <v>20.31</v>
       </c>
       <c r="M71">
-        <v>8.718743400000003</v>
+        <v>8.845102000000002</v>
       </c>
       <c r="N71">
-        <v>11.5912566</v>
+        <v>11.464898</v>
       </c>
       <c r="O71">
-        <v>2.202338753999999</v>
+        <v>2.178330619999999</v>
       </c>
       <c r="P71">
-        <v>9.388917845999996</v>
+        <v>9.286567379999997</v>
       </c>
       <c r="Q71">
-        <v>17.278917846</v>
+        <v>17.17656738</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.151561846049761</v>
+        <v>0.1548482654804706</v>
       </c>
       <c r="T71">
-        <v>1.937065352427552</v>
+        <v>1.99725727844383</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.329464128970694</v>
+        <v>2.296186069985399</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08943307964414118</v>
+        <v>0.08951736701285645</v>
       </c>
       <c r="C72">
-        <v>40.67524514031768</v>
+        <v>38.89796356090778</v>
       </c>
       <c r="D72">
-        <v>148.7252451403177</v>
+        <v>148.6149635609078</v>
       </c>
       <c r="E72">
-        <v>84.79000000000002</v>
+        <v>86.45700000000002</v>
       </c>
       <c r="F72">
-        <v>116.69</v>
+        <v>118.357</v>
       </c>
       <c r="G72">
         <v>8.640000000000001</v>
@@ -7191,28 +7191,28 @@
         <v>20.31</v>
       </c>
       <c r="M72">
-        <v>8.845102000000002</v>
+        <v>8.971460600000002</v>
       </c>
       <c r="N72">
-        <v>11.464898</v>
+        <v>11.3385394</v>
       </c>
       <c r="O72">
-        <v>2.178330619999999</v>
+        <v>2.154322485999999</v>
       </c>
       <c r="P72">
-        <v>9.286567379999997</v>
+        <v>9.184216913999997</v>
       </c>
       <c r="Q72">
-        <v>17.17656738</v>
+        <v>17.074216914</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1548482654804706</v>
+        <v>0.1583613345270912</v>
       </c>
       <c r="T72">
-        <v>1.99725727844383</v>
+        <v>2.061600371771576</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.296186069985399</v>
+        <v>2.263845421112365</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08951736701285645</v>
+        <v>0.08960165438157171</v>
       </c>
       <c r="C73">
-        <v>38.89796356090781</v>
+        <v>37.1208454105801</v>
       </c>
       <c r="D73">
-        <v>148.6149635609078</v>
+        <v>148.5048454105801</v>
       </c>
       <c r="E73">
-        <v>86.45699999999999</v>
+        <v>88.124</v>
       </c>
       <c r="F73">
-        <v>118.357</v>
+        <v>120.024</v>
       </c>
       <c r="G73">
         <v>8.640000000000001</v>
@@ -7273,28 +7273,28 @@
         <v>20.31</v>
       </c>
       <c r="M73">
-        <v>8.9714606</v>
+        <v>9.0978192</v>
       </c>
       <c r="N73">
-        <v>11.3385394</v>
+        <v>11.2121808</v>
       </c>
       <c r="O73">
-        <v>2.154322486</v>
+        <v>2.130314352</v>
       </c>
       <c r="P73">
-        <v>9.184216913999999</v>
+        <v>9.081866448</v>
       </c>
       <c r="Q73">
-        <v>17.074216914</v>
+        <v>16.971866448</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1583613345270912</v>
+        <v>0.1621253370770418</v>
       </c>
       <c r="T73">
-        <v>2.061600371771575</v>
+        <v>2.130539400337017</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.263845421112366</v>
+        <v>2.232403123596916</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08960165438157171</v>
+        <v>0.08968594175028696</v>
       </c>
       <c r="C74">
-        <v>37.1208454105801</v>
+        <v>35.34389032631881</v>
       </c>
       <c r="D74">
-        <v>148.5048454105801</v>
+        <v>148.3948903263188</v>
       </c>
       <c r="E74">
-        <v>88.124</v>
+        <v>89.791</v>
       </c>
       <c r="F74">
-        <v>120.024</v>
+        <v>121.691</v>
       </c>
       <c r="G74">
         <v>8.640000000000001</v>
@@ -7355,28 +7355,28 @@
         <v>20.31</v>
       </c>
       <c r="M74">
-        <v>9.0978192</v>
+        <v>9.224177800000001</v>
       </c>
       <c r="N74">
-        <v>11.2121808</v>
+        <v>11.0858222</v>
       </c>
       <c r="O74">
-        <v>2.130314352</v>
+        <v>2.106306217999999</v>
       </c>
       <c r="P74">
-        <v>9.081866448</v>
+        <v>8.979515981999999</v>
       </c>
       <c r="Q74">
-        <v>16.971866448</v>
+        <v>16.869515982</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1621253370770418</v>
+        <v>0.1661681546306925</v>
       </c>
       <c r="T74">
-        <v>2.130539400337017</v>
+        <v>2.204585023611009</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.232403123596916</v>
+        <v>2.201822258890109</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08968594175028696</v>
+        <v>0.08977022911900223</v>
       </c>
       <c r="C75">
-        <v>35.34389032631881</v>
+        <v>33.5670979461828</v>
       </c>
       <c r="D75">
-        <v>148.3948903263188</v>
+        <v>148.2850979461828</v>
       </c>
       <c r="E75">
-        <v>89.791</v>
+        <v>91.458</v>
       </c>
       <c r="F75">
-        <v>121.691</v>
+        <v>123.358</v>
       </c>
       <c r="G75">
         <v>8.640000000000001</v>
@@ -7437,28 +7437,28 @@
         <v>20.31</v>
       </c>
       <c r="M75">
-        <v>9.224177800000001</v>
+        <v>9.350536400000001</v>
       </c>
       <c r="N75">
-        <v>11.0858222</v>
+        <v>10.9594636</v>
       </c>
       <c r="O75">
-        <v>2.106306217999999</v>
+        <v>2.082298084</v>
       </c>
       <c r="P75">
-        <v>8.979515981999999</v>
+        <v>8.877165515999998</v>
       </c>
       <c r="Q75">
-        <v>16.869515982</v>
+        <v>16.767165516</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1661681546306925</v>
+        <v>0.1705219581500085</v>
       </c>
       <c r="T75">
-        <v>2.204585023611009</v>
+        <v>2.284326464059924</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.201822258890109</v>
+        <v>2.172067904040243</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08977022911900223</v>
+        <v>0.0898545164877175</v>
       </c>
       <c r="C76">
-        <v>33.5670979461828</v>
+        <v>31.79046790930104</v>
       </c>
       <c r="D76">
-        <v>148.2850979461828</v>
+        <v>148.175467909301</v>
       </c>
       <c r="E76">
-        <v>91.458</v>
+        <v>93.125</v>
       </c>
       <c r="F76">
-        <v>123.358</v>
+        <v>125.025</v>
       </c>
       <c r="G76">
         <v>8.640000000000001</v>
@@ -7519,28 +7519,28 @@
         <v>20.31</v>
       </c>
       <c r="M76">
-        <v>9.350536400000001</v>
+        <v>9.476895000000001</v>
       </c>
       <c r="N76">
-        <v>10.9594636</v>
+        <v>10.833105</v>
       </c>
       <c r="O76">
-        <v>2.082298084</v>
+        <v>2.05828995</v>
       </c>
       <c r="P76">
-        <v>8.877165515999998</v>
+        <v>8.774815049999997</v>
       </c>
       <c r="Q76">
-        <v>16.767165516</v>
+        <v>16.66481505</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1705219581500085</v>
+        <v>0.17522406595087</v>
       </c>
       <c r="T76">
-        <v>2.284326464059924</v>
+        <v>2.370447219744753</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.172067904040243</v>
+        <v>2.14310699865304</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0898545164877175</v>
+        <v>0.08993880385643276</v>
       </c>
       <c r="C77">
-        <v>31.79046790930104</v>
+        <v>30.01399985586907</v>
       </c>
       <c r="D77">
-        <v>148.175467909301</v>
+        <v>148.0659998558691</v>
       </c>
       <c r="E77">
-        <v>93.125</v>
+        <v>94.79200000000003</v>
       </c>
       <c r="F77">
-        <v>125.025</v>
+        <v>126.692</v>
       </c>
       <c r="G77">
         <v>8.640000000000001</v>
@@ -7601,28 +7601,28 @@
         <v>20.31</v>
       </c>
       <c r="M77">
-        <v>9.476895000000001</v>
+        <v>9.603253600000002</v>
       </c>
       <c r="N77">
-        <v>10.833105</v>
+        <v>10.7067464</v>
       </c>
       <c r="O77">
-        <v>2.05828995</v>
+        <v>2.034281816</v>
       </c>
       <c r="P77">
-        <v>8.774815049999997</v>
+        <v>8.672464583999997</v>
       </c>
       <c r="Q77">
-        <v>16.66481505</v>
+        <v>16.562464584</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.17522406595087</v>
+        <v>0.1803180160684698</v>
       </c>
       <c r="T77">
-        <v>2.370447219744753</v>
+        <v>2.463744705069984</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.14310699865304</v>
+        <v>2.114908222354973</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08993880385643276</v>
+        <v>0.09002309122514801</v>
       </c>
       <c r="C78">
-        <v>30.01399985586907</v>
+        <v>28.23769342714499</v>
       </c>
       <c r="D78">
-        <v>148.0659998558691</v>
+        <v>147.956693427145</v>
       </c>
       <c r="E78">
-        <v>94.79200000000003</v>
+        <v>96.459</v>
       </c>
       <c r="F78">
-        <v>126.692</v>
+        <v>128.359</v>
       </c>
       <c r="G78">
         <v>8.640000000000001</v>
@@ -7683,28 +7683,28 @@
         <v>20.31</v>
       </c>
       <c r="M78">
-        <v>9.603253600000002</v>
+        <v>9.729612200000002</v>
       </c>
       <c r="N78">
-        <v>10.7067464</v>
+        <v>10.5803878</v>
       </c>
       <c r="O78">
-        <v>2.034281816</v>
+        <v>2.010273681999999</v>
       </c>
       <c r="P78">
-        <v>8.672464583999997</v>
+        <v>8.570114117999998</v>
       </c>
       <c r="Q78">
-        <v>16.562464584</v>
+        <v>16.460114118</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1803180160684698</v>
+        <v>0.1858549183702088</v>
       </c>
       <c r="T78">
-        <v>2.463744705069984</v>
+        <v>2.565155015206105</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.114908222354973</v>
+        <v>2.087441881804908</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09002309122514801</v>
+        <v>0.09010737859386328</v>
       </c>
       <c r="C79">
-        <v>28.23769342714499</v>
+        <v>26.46154826544517</v>
       </c>
       <c r="D79">
-        <v>147.956693427145</v>
+        <v>147.8475482654452</v>
       </c>
       <c r="E79">
-        <v>96.459</v>
+        <v>98.126</v>
       </c>
       <c r="F79">
-        <v>128.359</v>
+        <v>130.026</v>
       </c>
       <c r="G79">
         <v>8.640000000000001</v>
@@ -7765,28 +7765,28 @@
         <v>20.31</v>
       </c>
       <c r="M79">
-        <v>9.729612200000002</v>
+        <v>9.855970800000001</v>
       </c>
       <c r="N79">
-        <v>10.5803878</v>
+        <v>10.4540292</v>
       </c>
       <c r="O79">
-        <v>2.010273681999999</v>
+        <v>1.986265548</v>
       </c>
       <c r="P79">
-        <v>8.570114117999998</v>
+        <v>8.467763651999999</v>
       </c>
       <c r="Q79">
-        <v>16.460114118</v>
+        <v>16.357763652</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1858549183702088</v>
+        <v>0.1918951754266512</v>
       </c>
       <c r="T79">
-        <v>2.565155015206105</v>
+        <v>2.675784444445509</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.087441881804908</v>
+        <v>2.060679806397153</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09010737859386328</v>
+        <v>0.09019166596257853</v>
       </c>
       <c r="C80">
-        <v>26.46154826544517</v>
+        <v>24.68556401414085</v>
       </c>
       <c r="D80">
-        <v>147.8475482654452</v>
+        <v>147.7385640141409</v>
       </c>
       <c r="E80">
-        <v>98.126</v>
+        <v>99.79300000000001</v>
       </c>
       <c r="F80">
-        <v>130.026</v>
+        <v>131.693</v>
       </c>
       <c r="G80">
         <v>8.640000000000001</v>
@@ -7847,28 +7847,28 @@
         <v>20.31</v>
       </c>
       <c r="M80">
-        <v>9.855970800000001</v>
+        <v>9.982329400000001</v>
       </c>
       <c r="N80">
-        <v>10.4540292</v>
+        <v>10.3276706</v>
       </c>
       <c r="O80">
-        <v>1.986265548</v>
+        <v>1.962257414</v>
       </c>
       <c r="P80">
-        <v>8.467763651999999</v>
+        <v>8.365413185999998</v>
       </c>
       <c r="Q80">
-        <v>16.357763652</v>
+        <v>16.255413186</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1918951754266512</v>
+        <v>0.1985106950598978</v>
       </c>
       <c r="T80">
-        <v>2.675784444445509</v>
+        <v>2.796950009802952</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.060679806397153</v>
+        <v>2.034595251885797</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09019166596257853</v>
+        <v>0.09027595333129379</v>
       </c>
       <c r="C81">
-        <v>24.68556401414085</v>
+        <v>22.90974031765393</v>
       </c>
       <c r="D81">
-        <v>147.7385640141409</v>
+        <v>147.629740317654</v>
       </c>
       <c r="E81">
-        <v>99.79300000000001</v>
+        <v>101.46</v>
       </c>
       <c r="F81">
-        <v>131.693</v>
+        <v>133.36</v>
       </c>
       <c r="G81">
         <v>8.640000000000001</v>
@@ -7929,28 +7929,28 @@
         <v>20.31</v>
       </c>
       <c r="M81">
-        <v>9.982329400000001</v>
+        <v>10.108688</v>
       </c>
       <c r="N81">
-        <v>10.3276706</v>
+        <v>10.201312</v>
       </c>
       <c r="O81">
-        <v>1.962257414</v>
+        <v>1.938249279999999</v>
       </c>
       <c r="P81">
-        <v>8.365413185999998</v>
+        <v>8.263062719999997</v>
       </c>
       <c r="Q81">
-        <v>16.255413186</v>
+        <v>16.15306272</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1985106950598978</v>
+        <v>0.205787766656469</v>
       </c>
       <c r="T81">
-        <v>2.796950009802952</v>
+        <v>2.930232131696139</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.034595251885797</v>
+        <v>2.009162811237224</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09027595333129379</v>
+        <v>0.09967686070000906</v>
       </c>
       <c r="C82">
-        <v>22.90974031765393</v>
+        <v>10.03492297580121</v>
       </c>
       <c r="D82">
-        <v>147.629740317654</v>
+        <v>136.4219229758012</v>
       </c>
       <c r="E82">
-        <v>101.46</v>
+        <v>103.127</v>
       </c>
       <c r="F82">
-        <v>133.36</v>
+        <v>135.027</v>
       </c>
       <c r="G82">
         <v>8.640000000000001</v>
@@ -8011,45 +8011,45 @@
         <v>20.31</v>
       </c>
       <c r="M82">
-        <v>10.108688</v>
+        <v>12.15243</v>
       </c>
       <c r="N82">
-        <v>10.201312</v>
+        <v>8.157569999999998</v>
       </c>
       <c r="O82">
-        <v>1.938249279999999</v>
+        <v>1.5499383</v>
       </c>
       <c r="P82">
-        <v>8.263062719999997</v>
+        <v>6.607631699999999</v>
       </c>
       <c r="Q82">
-        <v>16.15306272</v>
+        <v>14.4976317</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.205787766656469</v>
+        <v>0.2138308457895214</v>
       </c>
       <c r="T82">
-        <v>2.930232131696139</v>
+        <v>3.077543950630714</v>
       </c>
       <c r="U82">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V82">
         <v>0.19</v>
       </c>
       <c r="W82">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.009162811237224</v>
+        <v>1.671270684134778</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09967686070000906</v>
+        <v>0.09987616806872432</v>
       </c>
       <c r="C83">
-        <v>10.03492297580121</v>
+        <v>8.14869978886162</v>
       </c>
       <c r="D83">
-        <v>136.4219229758012</v>
+        <v>136.2026997888617</v>
       </c>
       <c r="E83">
-        <v>103.127</v>
+        <v>104.794</v>
       </c>
       <c r="F83">
-        <v>135.027</v>
+        <v>136.694</v>
       </c>
       <c r="G83">
         <v>8.640000000000001</v>
@@ -8093,28 +8093,28 @@
         <v>20.31</v>
       </c>
       <c r="M83">
-        <v>12.15243</v>
+        <v>12.30246</v>
       </c>
       <c r="N83">
-        <v>8.157569999999998</v>
+        <v>8.007539999999997</v>
       </c>
       <c r="O83">
-        <v>1.5499383</v>
+        <v>1.521432599999999</v>
       </c>
       <c r="P83">
-        <v>6.607631699999999</v>
+        <v>6.486107399999998</v>
       </c>
       <c r="Q83">
-        <v>14.4976317</v>
+        <v>14.3761074</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2138308457895214</v>
+        <v>0.2227676003818018</v>
       </c>
       <c r="T83">
-        <v>3.077543950630714</v>
+        <v>3.241223749446908</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.671270684134778</v>
+        <v>1.650889334328256</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09987616806872432</v>
+        <v>0.1000754754374396</v>
       </c>
       <c r="C84">
-        <v>8.14869978886162</v>
+        <v>6.263180032873066</v>
       </c>
       <c r="D84">
-        <v>136.2026997888617</v>
+        <v>135.9841800328731</v>
       </c>
       <c r="E84">
-        <v>104.794</v>
+        <v>106.461</v>
       </c>
       <c r="F84">
-        <v>136.694</v>
+        <v>138.361</v>
       </c>
       <c r="G84">
         <v>8.640000000000001</v>
@@ -8175,28 +8175,28 @@
         <v>20.31</v>
       </c>
       <c r="M84">
-        <v>12.30246</v>
+        <v>12.45249</v>
       </c>
       <c r="N84">
-        <v>8.007539999999997</v>
+        <v>7.857509999999998</v>
       </c>
       <c r="O84">
-        <v>1.521432599999999</v>
+        <v>1.4929269</v>
       </c>
       <c r="P84">
-        <v>6.486107399999998</v>
+        <v>6.364583099999998</v>
       </c>
       <c r="Q84">
-        <v>14.3761074</v>
+        <v>14.2545831</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2227676003818018</v>
+        <v>0.2327557378672917</v>
       </c>
       <c r="T84">
-        <v>3.241223749446908</v>
+        <v>3.424159995182655</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.650889334328256</v>
+        <v>1.630999101384542</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1000754754374396</v>
+        <v>0.1002747828061548</v>
       </c>
       <c r="C85">
-        <v>6.263180032873066</v>
+        <v>4.378360327564451</v>
       </c>
       <c r="D85">
-        <v>135.9841800328731</v>
+        <v>135.7663603275645</v>
       </c>
       <c r="E85">
-        <v>106.461</v>
+        <v>108.128</v>
       </c>
       <c r="F85">
-        <v>138.361</v>
+        <v>140.028</v>
       </c>
       <c r="G85">
         <v>8.640000000000001</v>
@@ -8257,28 +8257,28 @@
         <v>20.31</v>
       </c>
       <c r="M85">
-        <v>12.45249</v>
+        <v>12.60252</v>
       </c>
       <c r="N85">
-        <v>7.857509999999998</v>
+        <v>7.707479999999997</v>
       </c>
       <c r="O85">
-        <v>1.4929269</v>
+        <v>1.464421199999999</v>
       </c>
       <c r="P85">
-        <v>6.364583099999998</v>
+        <v>6.243058799999997</v>
       </c>
       <c r="Q85">
-        <v>14.2545831</v>
+        <v>14.1330588</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2327557378672917</v>
+        <v>0.2439923925384678</v>
       </c>
       <c r="T85">
-        <v>3.424159995182655</v>
+        <v>3.629963271635371</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.630999101384542</v>
+        <v>1.611582445415678</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1002747828061548</v>
+        <v>0.1004740901748701</v>
       </c>
       <c r="C86">
-        <v>4.378360327564451</v>
+        <v>2.494237314288483</v>
       </c>
       <c r="D86">
-        <v>135.7663603275645</v>
+        <v>135.5492373142885</v>
       </c>
       <c r="E86">
-        <v>108.128</v>
+        <v>109.795</v>
       </c>
       <c r="F86">
-        <v>140.028</v>
+        <v>141.695</v>
       </c>
       <c r="G86">
         <v>8.640000000000001</v>
@@ -8339,28 +8339,28 @@
         <v>20.31</v>
       </c>
       <c r="M86">
-        <v>12.60252</v>
+        <v>12.75255</v>
       </c>
       <c r="N86">
-        <v>7.707479999999997</v>
+        <v>7.557449999999998</v>
       </c>
       <c r="O86">
-        <v>1.464421199999999</v>
+        <v>1.435915499999999</v>
       </c>
       <c r="P86">
-        <v>6.243058799999997</v>
+        <v>6.121534499999998</v>
       </c>
       <c r="Q86">
-        <v>14.1330588</v>
+        <v>14.0115345</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2439923925384677</v>
+        <v>0.2567272678324673</v>
       </c>
       <c r="T86">
-        <v>3.629963271635368</v>
+        <v>3.863206984948446</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.611582445415678</v>
+        <v>1.5926226519402</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1004740901748701</v>
+        <v>0.1006733975435854</v>
       </c>
       <c r="C87">
-        <v>2.494237314288483</v>
+        <v>0.6108076558485322</v>
       </c>
       <c r="D87">
-        <v>135.5492373142885</v>
+        <v>135.3328076558486</v>
       </c>
       <c r="E87">
-        <v>109.795</v>
+        <v>111.462</v>
       </c>
       <c r="F87">
-        <v>141.695</v>
+        <v>143.362</v>
       </c>
       <c r="G87">
         <v>8.640000000000001</v>
@@ -8421,28 +8421,28 @@
         <v>20.31</v>
       </c>
       <c r="M87">
-        <v>12.75255</v>
+        <v>12.90258</v>
       </c>
       <c r="N87">
-        <v>7.557449999999998</v>
+        <v>7.407419999999997</v>
       </c>
       <c r="O87">
-        <v>1.435915499999999</v>
+        <v>1.407409799999999</v>
       </c>
       <c r="P87">
-        <v>6.121534499999998</v>
+        <v>6.000010199999998</v>
       </c>
       <c r="Q87">
-        <v>14.0115345</v>
+        <v>13.8900102</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2567272678324673</v>
+        <v>0.2712814110256097</v>
       </c>
       <c r="T87">
-        <v>3.863206984948446</v>
+        <v>4.129771228734819</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.5926226519402</v>
+        <v>1.574103783894384</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1006733975435854</v>
+        <v>0.1008727049123006</v>
       </c>
       <c r="C88">
-        <v>0.6108076558485322</v>
+        <v>-1.271931963672245</v>
       </c>
       <c r="D88">
-        <v>135.3328076558486</v>
+        <v>135.1170680363278</v>
       </c>
       <c r="E88">
-        <v>111.462</v>
+        <v>113.129</v>
       </c>
       <c r="F88">
-        <v>143.362</v>
+        <v>145.029</v>
       </c>
       <c r="G88">
         <v>8.640000000000001</v>
@@ -8503,28 +8503,28 @@
         <v>20.31</v>
       </c>
       <c r="M88">
-        <v>12.90258</v>
+        <v>13.05261</v>
       </c>
       <c r="N88">
-        <v>7.407419999999997</v>
+        <v>7.257389999999997</v>
       </c>
       <c r="O88">
-        <v>1.407409799999999</v>
+        <v>1.3789041</v>
       </c>
       <c r="P88">
-        <v>6.000010199999998</v>
+        <v>5.878485899999998</v>
       </c>
       <c r="Q88">
-        <v>13.8900102</v>
+        <v>13.7684859</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2712814110256097</v>
+        <v>0.2880746531715432</v>
       </c>
       <c r="T88">
-        <v>4.129771228734819</v>
+        <v>4.437345356180635</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.574103783894384</v>
+        <v>1.556010636953069</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1008727049123006</v>
+        <v>0.1010720122810159</v>
       </c>
       <c r="C89">
-        <v>-1.271931963672245</v>
+        <v>-3.15398483908001</v>
       </c>
       <c r="D89">
-        <v>135.1170680363278</v>
+        <v>134.90201516092</v>
       </c>
       <c r="E89">
-        <v>113.129</v>
+        <v>114.796</v>
       </c>
       <c r="F89">
-        <v>145.029</v>
+        <v>146.696</v>
       </c>
       <c r="G89">
         <v>8.640000000000001</v>
@@ -8585,28 +8585,28 @@
         <v>20.31</v>
       </c>
       <c r="M89">
-        <v>13.05261</v>
+        <v>13.20264</v>
       </c>
       <c r="N89">
-        <v>7.257389999999997</v>
+        <v>7.107359999999996</v>
       </c>
       <c r="O89">
-        <v>1.3789041</v>
+        <v>1.350398399999999</v>
       </c>
       <c r="P89">
-        <v>5.878485899999998</v>
+        <v>5.756961599999997</v>
       </c>
       <c r="Q89">
-        <v>13.7684859</v>
+        <v>13.6469616</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2880746531715432</v>
+        <v>0.3076667690084657</v>
       </c>
       <c r="T89">
-        <v>4.437345356180635</v>
+        <v>4.796181838200755</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.556010636953069</v>
+        <v>1.538328697896784</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1010720122810159</v>
+        <v>0.1012713196497312</v>
       </c>
       <c r="C90">
-        <v>-3.15398483908001</v>
+        <v>-5.035354244238334</v>
       </c>
       <c r="D90">
-        <v>134.90201516092</v>
+        <v>134.6876457557617</v>
       </c>
       <c r="E90">
-        <v>114.796</v>
+        <v>116.463</v>
       </c>
       <c r="F90">
-        <v>146.696</v>
+        <v>148.363</v>
       </c>
       <c r="G90">
         <v>8.640000000000001</v>
@@ -8667,28 +8667,28 @@
         <v>20.31</v>
       </c>
       <c r="M90">
-        <v>13.20264</v>
+        <v>13.35267</v>
       </c>
       <c r="N90">
-        <v>7.107359999999996</v>
+        <v>6.957329999999997</v>
       </c>
       <c r="O90">
-        <v>1.350398399999999</v>
+        <v>1.321892699999999</v>
       </c>
       <c r="P90">
-        <v>5.756961599999997</v>
+        <v>5.635437299999998</v>
       </c>
       <c r="Q90">
-        <v>13.6469616</v>
+        <v>13.5254373</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3076667690084657</v>
+        <v>0.3308210877248286</v>
       </c>
       <c r="T90">
-        <v>4.796181838200755</v>
+        <v>5.220261316951803</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.538328697896784</v>
+        <v>1.521044105785584</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1012713196497312</v>
+        <v>0.1014706270184464</v>
       </c>
       <c r="C91">
-        <v>-5.035354244238334</v>
+        <v>-6.916043432234005</v>
       </c>
       <c r="D91">
-        <v>134.6876457557617</v>
+        <v>134.473956567766</v>
       </c>
       <c r="E91">
-        <v>116.463</v>
+        <v>118.13</v>
       </c>
       <c r="F91">
-        <v>148.363</v>
+        <v>150.03</v>
       </c>
       <c r="G91">
         <v>8.640000000000001</v>
@@ -8749,28 +8749,28 @@
         <v>20.31</v>
       </c>
       <c r="M91">
-        <v>13.35267</v>
+        <v>13.5027</v>
       </c>
       <c r="N91">
-        <v>6.957329999999997</v>
+        <v>6.807299999999996</v>
       </c>
       <c r="O91">
-        <v>1.321892699999999</v>
+        <v>1.293386999999999</v>
       </c>
       <c r="P91">
-        <v>5.635437299999998</v>
+        <v>5.513912999999997</v>
       </c>
       <c r="Q91">
-        <v>13.5254373</v>
+        <v>13.403913</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3308210877248286</v>
+        <v>0.3586062701844641</v>
       </c>
       <c r="T91">
-        <v>5.220261316951803</v>
+        <v>5.729156691453063</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.521044105785584</v>
+        <v>1.5041436157213</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1014706270184464</v>
+        <v>0.1463441138163665</v>
       </c>
       <c r="C92">
-        <v>-6.916043432234005</v>
+        <v>-43.97568693032075</v>
       </c>
       <c r="D92">
-        <v>134.473956567766</v>
+        <v>99.08131306967928</v>
       </c>
       <c r="E92">
-        <v>118.13</v>
+        <v>119.797</v>
       </c>
       <c r="F92">
-        <v>150.03</v>
+        <v>151.697</v>
       </c>
       <c r="G92">
         <v>8.640000000000001</v>
@@ -8831,45 +8831,45 @@
         <v>20.31</v>
       </c>
       <c r="M92">
-        <v>13.5027</v>
+        <v>22.26911960000001</v>
       </c>
       <c r="N92">
-        <v>6.807299999999996</v>
+        <v>-1.959119600000008</v>
       </c>
       <c r="O92">
-        <v>1.293386999999999</v>
+        <v>-0.3722327240000016</v>
       </c>
       <c r="P92">
-        <v>5.513912999999997</v>
+        <v>-1.586886876000007</v>
       </c>
       <c r="Q92">
-        <v>13.403913</v>
+        <v>6.303113123999993</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3586062701844641</v>
+        <v>0.3989431562479696</v>
       </c>
       <c r="T92">
-        <v>5.729156691453063</v>
+        <v>6.467940925435435</v>
       </c>
       <c r="U92">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.19</v>
+        <v>0.1732848028711471</v>
       </c>
       <c r="W92">
-        <v>0.07290000000000001</v>
+        <v>0.1213617909385156</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.5041436157213</v>
+        <v>0.9120252782691953</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1463441138163665</v>
+        <v>0.1473541138163665</v>
       </c>
       <c r="C93">
-        <v>-43.97568693032075</v>
+        <v>-46.22617638298472</v>
       </c>
       <c r="D93">
-        <v>99.08131306967928</v>
+        <v>98.49782361701531</v>
       </c>
       <c r="E93">
-        <v>119.797</v>
+        <v>121.464</v>
       </c>
       <c r="F93">
-        <v>151.697</v>
+        <v>153.364</v>
       </c>
       <c r="G93">
         <v>8.640000000000001</v>
@@ -8913,37 +8913,37 @@
         <v>20.31</v>
       </c>
       <c r="M93">
-        <v>22.26911960000001</v>
+        <v>22.51383520000001</v>
       </c>
       <c r="N93">
-        <v>-1.959119600000008</v>
+        <v>-2.203835200000007</v>
       </c>
       <c r="O93">
-        <v>-0.3722327240000016</v>
+        <v>-0.4187286880000014</v>
       </c>
       <c r="P93">
-        <v>-1.586886876000007</v>
+        <v>-1.785106512000006</v>
       </c>
       <c r="Q93">
-        <v>6.303113123999993</v>
+        <v>6.104893487999994</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3989431562479696</v>
+        <v>0.4430860507789659</v>
       </c>
       <c r="T93">
-        <v>6.467940925435435</v>
+        <v>7.276433541114867</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1732848028711471</v>
+        <v>0.1714012724051564</v>
       </c>
       <c r="W93">
-        <v>0.1213617909385156</v>
+        <v>0.1216382932109231</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9120252782691953</v>
+        <v>0.9021119600271389</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1473541138163665</v>
+        <v>0.1483641138163665</v>
       </c>
       <c r="C94">
-        <v>-46.22617638298472</v>
+        <v>-48.46983373579491</v>
       </c>
       <c r="D94">
-        <v>98.49782361701531</v>
+        <v>97.92116626420513</v>
       </c>
       <c r="E94">
-        <v>121.464</v>
+        <v>123.131</v>
       </c>
       <c r="F94">
-        <v>153.364</v>
+        <v>155.031</v>
       </c>
       <c r="G94">
         <v>8.640000000000001</v>
@@ -8995,37 +8995,37 @@
         <v>20.31</v>
       </c>
       <c r="M94">
-        <v>22.51383520000001</v>
+        <v>22.75855080000001</v>
       </c>
       <c r="N94">
-        <v>-2.203835200000007</v>
+        <v>-2.448550800000007</v>
       </c>
       <c r="O94">
-        <v>-0.4187286880000014</v>
+        <v>-0.4652246520000013</v>
       </c>
       <c r="P94">
-        <v>-1.785106512000006</v>
+        <v>-1.983326148000006</v>
       </c>
       <c r="Q94">
-        <v>6.104893487999994</v>
+        <v>5.906673851999994</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4430860507789659</v>
+        <v>0.4998412008902468</v>
       </c>
       <c r="T94">
-        <v>7.276433541114867</v>
+        <v>8.315924046988419</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1714012724051564</v>
+        <v>0.1695582479706924</v>
       </c>
       <c r="W94">
-        <v>0.1216382932109231</v>
+        <v>0.1219088491979024</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9021119600271389</v>
+        <v>0.8924118314246966</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1483641138163665</v>
+        <v>0.1493741138163664</v>
       </c>
       <c r="C95">
-        <v>-48.46983373579491</v>
+        <v>-50.70677828629118</v>
       </c>
       <c r="D95">
-        <v>97.92116626420513</v>
+        <v>97.35122171370885</v>
       </c>
       <c r="E95">
-        <v>123.131</v>
+        <v>124.798</v>
       </c>
       <c r="F95">
-        <v>155.031</v>
+        <v>156.698</v>
       </c>
       <c r="G95">
         <v>8.640000000000001</v>
@@ -9077,37 +9077,37 @@
         <v>20.31</v>
       </c>
       <c r="M95">
-        <v>22.75855080000001</v>
+        <v>23.00326640000001</v>
       </c>
       <c r="N95">
-        <v>-2.448550800000007</v>
+        <v>-2.693266400000009</v>
       </c>
       <c r="O95">
-        <v>-0.4652246520000013</v>
+        <v>-0.5117206160000018</v>
       </c>
       <c r="P95">
-        <v>-1.983326148000006</v>
+        <v>-2.181545784000008</v>
       </c>
       <c r="Q95">
-        <v>5.906673851999994</v>
+        <v>5.708454215999992</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4998412008902468</v>
+        <v>0.5755147343719547</v>
       </c>
       <c r="T95">
-        <v>8.315924046988419</v>
+        <v>9.701911388153158</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1695582479706924</v>
+        <v>0.1677544368220679</v>
       </c>
       <c r="W95">
-        <v>0.1219088491979024</v>
+        <v>0.1221736486745204</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8924118314246966</v>
+        <v>0.8829180885371997</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1493741138163664</v>
+        <v>0.1503841138163665</v>
       </c>
       <c r="C96">
-        <v>-50.70677828629118</v>
+        <v>-52.93712657062801</v>
       </c>
       <c r="D96">
-        <v>97.35122171370885</v>
+        <v>96.78787342937203</v>
       </c>
       <c r="E96">
-        <v>124.798</v>
+        <v>126.465</v>
       </c>
       <c r="F96">
-        <v>156.698</v>
+        <v>158.365</v>
       </c>
       <c r="G96">
         <v>8.640000000000001</v>
@@ -9159,37 +9159,37 @@
         <v>20.31</v>
       </c>
       <c r="M96">
-        <v>23.00326640000001</v>
+        <v>23.24798200000001</v>
       </c>
       <c r="N96">
-        <v>-2.693266400000009</v>
+        <v>-2.937982000000009</v>
       </c>
       <c r="O96">
-        <v>-0.5117206160000018</v>
+        <v>-0.5582165800000016</v>
       </c>
       <c r="P96">
-        <v>-2.181545784000008</v>
+        <v>-2.379765420000007</v>
       </c>
       <c r="Q96">
-        <v>5.708454215999992</v>
+        <v>5.510234579999993</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5755147343719547</v>
+        <v>0.681457681246346</v>
       </c>
       <c r="T96">
-        <v>9.701911388153158</v>
+        <v>11.6422936657838</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1677544368220679</v>
+        <v>0.1659886006449936</v>
       </c>
       <c r="W96">
-        <v>0.1221736486745204</v>
+        <v>0.122432873425315</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8829180885371997</v>
+        <v>0.8736242139210186</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1503841138163665</v>
+        <v>0.1513941138163665</v>
       </c>
       <c r="C97">
-        <v>-52.93712657062801</v>
+        <v>-55.16099244301175</v>
       </c>
       <c r="D97">
-        <v>96.78787342937203</v>
+        <v>96.23100755698829</v>
       </c>
       <c r="E97">
-        <v>126.465</v>
+        <v>128.132</v>
       </c>
       <c r="F97">
-        <v>158.365</v>
+        <v>160.032</v>
       </c>
       <c r="G97">
         <v>8.640000000000001</v>
@@ -9241,37 +9241,37 @@
         <v>20.31</v>
       </c>
       <c r="M97">
-        <v>23.24798200000001</v>
+        <v>23.49269760000001</v>
       </c>
       <c r="N97">
-        <v>-2.937982000000009</v>
+        <v>-3.182697600000008</v>
       </c>
       <c r="O97">
-        <v>-0.5582165800000016</v>
+        <v>-0.6047125440000015</v>
       </c>
       <c r="P97">
-        <v>-2.379765420000007</v>
+        <v>-2.577985056000006</v>
       </c>
       <c r="Q97">
-        <v>5.510234579999993</v>
+        <v>5.312014943999993</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.681457681246346</v>
+        <v>0.8403721015579327</v>
       </c>
       <c r="T97">
-        <v>11.6422936657838</v>
+        <v>14.55286708222975</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1659886006449936</v>
+        <v>0.1642595527216082</v>
       </c>
       <c r="W97">
-        <v>0.122432873425315</v>
+        <v>0.1226866976604679</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8736242139210186</v>
+        <v>0.8645239616926748</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1513941138163665</v>
+        <v>0.1524041138163665</v>
       </c>
       <c r="C98">
-        <v>-55.16099244301172</v>
+        <v>-57.37848715241226</v>
       </c>
       <c r="D98">
-        <v>96.23100755698829</v>
+        <v>95.68051284758775</v>
       </c>
       <c r="E98">
-        <v>128.132</v>
+        <v>129.799</v>
       </c>
       <c r="F98">
-        <v>160.032</v>
+        <v>161.699</v>
       </c>
       <c r="G98">
         <v>8.640000000000001</v>
@@ -9323,37 +9323,37 @@
         <v>20.31</v>
       </c>
       <c r="M98">
-        <v>23.4926976</v>
+        <v>23.7374132</v>
       </c>
       <c r="N98">
-        <v>-3.182697600000004</v>
+        <v>-3.427413200000004</v>
       </c>
       <c r="O98">
-        <v>-0.6047125440000009</v>
+        <v>-0.6512085080000007</v>
       </c>
       <c r="P98">
-        <v>-2.577985056000004</v>
+        <v>-2.776204692000003</v>
       </c>
       <c r="Q98">
-        <v>5.312014943999996</v>
+        <v>5.113795307999997</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8403721015579306</v>
+        <v>1.105229468743908</v>
       </c>
       <c r="T98">
-        <v>14.55286708222971</v>
+        <v>19.40382277630628</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1642595527216082</v>
+        <v>0.16256615527087</v>
       </c>
       <c r="W98">
-        <v>0.1226866976604679</v>
+        <v>0.1229352884062363</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.864523961692675</v>
+        <v>0.8556113435308947</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1524041138163665</v>
+        <v>0.1534141138163665</v>
       </c>
       <c r="C99">
-        <v>-57.37848715241226</v>
+        <v>-59.5897194166558</v>
       </c>
       <c r="D99">
-        <v>95.68051284758775</v>
+        <v>95.13628058334422</v>
       </c>
       <c r="E99">
-        <v>129.799</v>
+        <v>131.466</v>
       </c>
       <c r="F99">
-        <v>161.699</v>
+        <v>163.366</v>
       </c>
       <c r="G99">
         <v>8.640000000000001</v>
@@ -9405,37 +9405,37 @@
         <v>20.31</v>
       </c>
       <c r="M99">
-        <v>23.7374132</v>
+        <v>23.98212880000001</v>
       </c>
       <c r="N99">
-        <v>-3.427413200000004</v>
+        <v>-3.672128800000007</v>
       </c>
       <c r="O99">
-        <v>-0.6512085080000007</v>
+        <v>-0.6977044720000013</v>
       </c>
       <c r="P99">
-        <v>-2.776204692000003</v>
+        <v>-2.974424328000005</v>
       </c>
       <c r="Q99">
-        <v>5.113795307999997</v>
+        <v>4.915575671999994</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.105229468743908</v>
+        <v>1.634944203115861</v>
       </c>
       <c r="T99">
-        <v>19.40382277630628</v>
+        <v>29.10573416445942</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.16256615527087</v>
+        <v>0.1609073169517795</v>
       </c>
       <c r="W99">
-        <v>0.1229352884062363</v>
+        <v>0.1231788058714788</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8556113435308947</v>
+        <v>0.8468806155356815</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1534141138163665</v>
+        <v>0.1544241138163665</v>
       </c>
       <c r="C100">
-        <v>-59.5897194166558</v>
+        <v>-61.79479549400376</v>
       </c>
       <c r="D100">
-        <v>95.13628058334422</v>
+        <v>94.59820450599625</v>
       </c>
       <c r="E100">
-        <v>131.466</v>
+        <v>133.133</v>
       </c>
       <c r="F100">
-        <v>163.366</v>
+        <v>165.033</v>
       </c>
       <c r="G100">
         <v>8.640000000000001</v>
@@ -9487,37 +9487,37 @@
         <v>20.31</v>
       </c>
       <c r="M100">
-        <v>23.98212880000001</v>
+        <v>24.2268444</v>
       </c>
       <c r="N100">
-        <v>-3.672128800000007</v>
+        <v>-3.916844400000006</v>
       </c>
       <c r="O100">
-        <v>-0.6977044720000013</v>
+        <v>-0.7442004360000011</v>
       </c>
       <c r="P100">
-        <v>-2.974424328000005</v>
+        <v>-3.172643964000005</v>
       </c>
       <c r="Q100">
-        <v>4.915575671999994</v>
+        <v>4.717356035999995</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.634944203115861</v>
+        <v>3.224088406231723</v>
       </c>
       <c r="T100">
-        <v>29.10573416445942</v>
+        <v>58.21146832891885</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1609073169517795</v>
+        <v>0.1592819905179231</v>
       </c>
       <c r="W100">
-        <v>0.1231788058714788</v>
+        <v>0.1234174037919689</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8468806155356815</v>
+        <v>0.838326265883806</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1544241138163665</v>
-      </c>
-      <c r="C101">
-        <v>-61.79479549400376</v>
-      </c>
-      <c r="D101">
-        <v>94.59820450599625</v>
-      </c>
-      <c r="E101">
-        <v>133.133</v>
-      </c>
-      <c r="F101">
-        <v>165.033</v>
-      </c>
-      <c r="G101">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="H101">
-        <v>134.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>28.2</v>
-      </c>
-      <c r="K101">
-        <v>7.89</v>
-      </c>
-      <c r="L101">
-        <v>20.31</v>
-      </c>
-      <c r="M101">
-        <v>24.2268444</v>
-      </c>
-      <c r="N101">
-        <v>-3.916844400000006</v>
-      </c>
-      <c r="O101">
-        <v>-0.7442004360000011</v>
-      </c>
-      <c r="P101">
-        <v>-3.172643964000005</v>
-      </c>
-      <c r="Q101">
-        <v>4.717356035999995</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.224088406231723</v>
-      </c>
-      <c r="T101">
-        <v>58.21146832891885</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1592819905179231</v>
-      </c>
-      <c r="W101">
-        <v>0.1234174037919689</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.838326265883806</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
